--- a/Take Over/Anlage_8_Vorlage_Projektplan_GBW25.xlsx
+++ b/Take Over/Anlage_8_Vorlage_Projektplan_GBW25.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Unit KKW\Projekte - Maßnahmen\Games BW Förderung_DCF\20_GBW FörderRICHTLINIE\ANTRÄGE-VERTRÄGE-ANLAGEN\04_GBW Anlagen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\ScrewDriversMFG\Take Over\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299756E9-7B49-4054-87AB-C57463CCB7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="55800" yWindow="1815" windowWidth="19950" windowHeight="27375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROJEKTPLAN" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -22,6 +23,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Start-Datum</t>
   </si>
@@ -70,15 +74,27 @@
     <t xml:space="preserve">Bitte machen Sie Angaben zu den einzelnen Projektphasen. Benennen Sie relevante Phasen des Projekts sowie die geplante Laufzeit. Die Dauer der Wochen berechnet sich automatisch. 
 Ergänzen bzw. ändern Sie die Tabelle und die Bezeichnungen für die einzelnen Phasen nach Bedarf. Im Anlagen-Dokument haben Sie die Möglichkeit weitere Angaben zur Projektplanung zu machen. </t>
   </si>
+  <si>
+    <t>Core Development</t>
+  </si>
+  <si>
+    <t>Meta-Game &amp; Skills</t>
+  </si>
+  <si>
+    <t>Testing, Polishing</t>
+  </si>
+  <si>
+    <t>Feedback Open Beta</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -221,21 +237,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -251,14 +267,12 @@
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -296,7 +310,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -519,20 +539,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y977"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="14" customFormat="1" ht="33" customHeight="1"/>
-    <row r="2" spans="1:25" ht="12.75">
+    <row r="1" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>9</v>
@@ -561,16 +581,16 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:25" ht="15.75" customHeight="1">
+    <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -590,14 +610,14 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -617,14 +637,14 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5" spans="1:25" ht="15.75" customHeight="1">
+    <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -644,22 +664,22 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:25" ht="30" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -679,7 +699,7 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" spans="1:25" ht="15.75" customHeight="1">
+    <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -706,7 +726,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:25" s="15" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -733,14 +753,14 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -762,7 +782,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -797,14 +817,20 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="8">
+        <v>46235</v>
+      </c>
+      <c r="D12" s="8">
+        <v>46295</v>
+      </c>
       <c r="E12" s="6">
         <f>DATEDIF(C12,D12,"D")/7</f>
-        <v>0</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -827,14 +853,20 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46296</v>
+      </c>
+      <c r="D13" s="9">
+        <v>46340</v>
+      </c>
       <c r="E13" s="6">
         <f t="shared" ref="E13:E17" si="0">DATEDIF(C13,D13,"D")/7</f>
-        <v>0</v>
+        <v>6.2857142857142856</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -857,14 +889,20 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="9">
+        <v>46341</v>
+      </c>
+      <c r="D14" s="9">
+        <v>46432</v>
+      </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -887,14 +925,20 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46433</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46507</v>
+      </c>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.571428571428571</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -917,7 +961,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1">
+    <row r="16" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="5"/>
       <c r="C16" s="9"/>
@@ -947,7 +991,7 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75" customHeight="1">
+    <row r="17" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="7"/>
       <c r="C17" s="9"/>
@@ -977,7 +1021,7 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
     </row>
-    <row r="18" spans="1:25" ht="15.75" customHeight="1">
+    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="13" t="s">
         <v>8</v>
@@ -986,7 +1030,7 @@
       <c r="D18" s="8"/>
       <c r="E18" s="6">
         <f>SUM(E12:E17)</f>
-        <v>0</v>
+        <v>38.428571428571431</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1009,7 +1053,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75" customHeight="1">
+    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1036,7 +1080,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.75" customHeight="1">
+    <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1063,7 +1107,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21" spans="1:25" ht="15.75" customHeight="1">
+    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1090,12 +1134,12 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" spans="1:25" ht="15.75" customHeight="1">
+    <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1119,7 +1163,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" spans="1:25" ht="15.75" customHeight="1">
+    <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="10" t="s">
         <v>4</v>
@@ -1150,7 +1194,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" spans="1:25" ht="15.75" customHeight="1">
+    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="10" t="s">
         <v>6</v>
@@ -1181,7 +1225,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1208,7 +1252,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="12.75">
+    <row r="26" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1235,7 +1279,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="12.75">
+    <row r="27" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1262,7 +1306,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="12.75">
+    <row r="28" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1289,7 +1333,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="12.75">
+    <row r="29" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1316,7 +1360,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="12.75">
+    <row r="30" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1343,7 +1387,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="1:25" ht="12.75">
+    <row r="31" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1370,7 +1414,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="12.75">
+    <row r="32" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1397,7 +1441,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" spans="1:25" ht="12.75">
+    <row r="33" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1424,7 +1468,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" spans="1:25" ht="12.75">
+    <row r="34" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1451,7 +1495,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" spans="1:25" ht="12.75">
+    <row r="35" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1478,7 +1522,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:25" ht="12.75">
+    <row r="36" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1505,7 +1549,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" spans="1:25" ht="12.75">
+    <row r="37" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1532,7 +1576,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:25" ht="12.75">
+    <row r="38" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1559,7 +1603,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" ht="12.75">
+    <row r="39" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1586,7 +1630,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" spans="1:25" ht="12.75">
+    <row r="40" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1613,7 +1657,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" spans="1:25" ht="12.75">
+    <row r="41" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1640,7 +1684,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42" spans="1:25" ht="12.75">
+    <row r="42" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1667,7 +1711,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" spans="1:25" ht="12.75">
+    <row r="43" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1694,7 +1738,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25" ht="12.75">
+    <row r="44" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1721,7 +1765,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" spans="1:25" ht="12.75">
+    <row r="45" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1748,7 +1792,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" spans="1:25" ht="12.75">
+    <row r="46" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1775,7 +1819,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47" spans="1:25" ht="12.75">
+    <row r="47" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1802,7 +1846,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" spans="1:25" ht="12.75">
+    <row r="48" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1829,7 +1873,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25" ht="12.75">
+    <row r="49" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1856,7 +1900,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50" spans="1:25" ht="12.75">
+    <row r="50" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1883,7 +1927,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" spans="1:25" ht="12.75">
+    <row r="51" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1910,7 +1954,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" spans="1:25" ht="12.75">
+    <row r="52" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1937,7 +1981,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" spans="1:25" ht="12.75">
+    <row r="53" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1964,7 +2008,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" spans="1:25" ht="12.75">
+    <row r="54" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1991,7 +2035,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" spans="1:25" ht="12.75">
+    <row r="55" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2018,7 +2062,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56" spans="1:25" ht="12.75">
+    <row r="56" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2045,7 +2089,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57" spans="1:25" ht="12.75">
+    <row r="57" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2072,7 +2116,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" spans="1:25" ht="12.75">
+    <row r="58" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2099,7 +2143,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" spans="1:25" ht="12.75">
+    <row r="59" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2126,7 +2170,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" spans="1:25" ht="12.75">
+    <row r="60" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2153,7 +2197,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="12.75">
+    <row r="61" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2180,7 +2224,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" spans="1:25" ht="12.75">
+    <row r="62" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2207,7 +2251,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" spans="1:25" ht="12.75">
+    <row r="63" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2234,7 +2278,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" spans="1:25" ht="12.75">
+    <row r="64" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2261,7 +2305,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" spans="1:25" ht="12.75">
+    <row r="65" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2288,7 +2332,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" spans="1:25" ht="12.75">
+    <row r="66" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2315,7 +2359,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" spans="1:25" ht="12.75">
+    <row r="67" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2342,7 +2386,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" spans="1:25" ht="12.75">
+    <row r="68" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2369,7 +2413,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" spans="1:25" ht="12.75">
+    <row r="69" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2396,7 +2440,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" spans="1:25" ht="12.75">
+    <row r="70" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2423,7 +2467,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" spans="1:25" ht="12.75">
+    <row r="71" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2450,7 +2494,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" spans="1:25" ht="12.75">
+    <row r="72" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2477,7 +2521,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" spans="1:25" ht="12.75">
+    <row r="73" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2504,7 +2548,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:25" ht="12.75">
+    <row r="74" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2531,7 +2575,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" spans="1:25" ht="12.75">
+    <row r="75" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2558,7 +2602,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76" spans="1:25" ht="12.75">
+    <row r="76" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2585,7 +2629,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77" spans="1:25" ht="12.75">
+    <row r="77" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2612,7 +2656,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78" spans="1:25" ht="12.75">
+    <row r="78" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2639,7 +2683,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" spans="1:25" ht="12.75">
+    <row r="79" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2666,7 +2710,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80" spans="1:25" ht="12.75">
+    <row r="80" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2693,7 +2737,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" spans="1:25" ht="12.75">
+    <row r="81" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2720,7 +2764,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" spans="1:25" ht="12.75">
+    <row r="82" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2747,7 +2791,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" spans="1:25" ht="12.75">
+    <row r="83" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2774,7 +2818,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" spans="1:25" ht="12.75">
+    <row r="84" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2801,7 +2845,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" spans="1:25" ht="12.75">
+    <row r="85" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2828,7 +2872,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" spans="1:25" ht="12.75">
+    <row r="86" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2855,7 +2899,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" spans="1:25" ht="12.75">
+    <row r="87" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2882,7 +2926,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" spans="1:25" ht="12.75">
+    <row r="88" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2909,7 +2953,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89" spans="1:25" ht="12.75">
+    <row r="89" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2936,7 +2980,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" spans="1:25" ht="12.75">
+    <row r="90" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2963,7 +3007,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91" spans="1:25" ht="12.75">
+    <row r="91" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2990,7 +3034,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" spans="1:25" ht="12.75">
+    <row r="92" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3017,7 +3061,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" spans="1:25" ht="12.75">
+    <row r="93" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3044,7 +3088,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" spans="1:25" ht="12.75">
+    <row r="94" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3071,7 +3115,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25" ht="12.75">
+    <row r="95" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3098,7 +3142,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" spans="1:25" ht="12.75">
+    <row r="96" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3125,7 +3169,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" spans="1:25" ht="12.75">
+    <row r="97" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3152,7 +3196,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" spans="1:25" ht="12.75">
+    <row r="98" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3179,7 +3223,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" spans="1:25" ht="12.75">
+    <row r="99" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3206,7 +3250,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" spans="1:25" ht="12.75">
+    <row r="100" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3233,7 +3277,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" spans="1:25" ht="12.75">
+    <row r="101" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3260,7 +3304,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" spans="1:25" ht="12.75">
+    <row r="102" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3287,7 +3331,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" spans="1:25" ht="12.75">
+    <row r="103" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3314,7 +3358,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" spans="1:25" ht="12.75">
+    <row r="104" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3341,7 +3385,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" spans="1:25" ht="12.75">
+    <row r="105" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3368,7 +3412,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" spans="1:25" ht="12.75">
+    <row r="106" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3395,7 +3439,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" spans="1:25" ht="12.75">
+    <row r="107" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3422,7 +3466,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" spans="1:25" ht="12.75">
+    <row r="108" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3449,7 +3493,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" spans="1:25" ht="12.75">
+    <row r="109" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3476,7 +3520,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" spans="1:25" ht="12.75">
+    <row r="110" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3503,7 +3547,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" spans="1:25" ht="12.75">
+    <row r="111" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3530,7 +3574,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" spans="1:25" ht="12.75">
+    <row r="112" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3557,7 +3601,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" spans="1:25" ht="12.75">
+    <row r="113" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3584,7 +3628,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" spans="1:25" ht="12.75">
+    <row r="114" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3611,7 +3655,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" spans="1:25" ht="12.75">
+    <row r="115" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3638,7 +3682,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" spans="1:25" ht="12.75">
+    <row r="116" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3665,7 +3709,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" spans="1:25" ht="12.75">
+    <row r="117" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3692,7 +3736,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" spans="1:25" ht="12.75">
+    <row r="118" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3719,7 +3763,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" spans="1:25" ht="12.75">
+    <row r="119" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3746,7 +3790,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" spans="1:25" ht="12.75">
+    <row r="120" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3773,7 +3817,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" spans="1:25" ht="12.75">
+    <row r="121" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3800,7 +3844,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" spans="1:25" ht="12.75">
+    <row r="122" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3827,7 +3871,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" spans="1:25" ht="12.75">
+    <row r="123" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3854,7 +3898,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" spans="1:25" ht="12.75">
+    <row r="124" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3881,7 +3925,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" spans="1:25" ht="12.75">
+    <row r="125" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3908,7 +3952,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" spans="1:25" ht="12.75">
+    <row r="126" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3935,7 +3979,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" spans="1:25" ht="12.75">
+    <row r="127" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3962,7 +4006,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" spans="1:25" ht="12.75">
+    <row r="128" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3989,7 +4033,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" spans="1:25" ht="12.75">
+    <row r="129" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4016,7 +4060,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" spans="1:25" ht="12.75">
+    <row r="130" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4043,7 +4087,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" spans="1:25" ht="12.75">
+    <row r="131" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4070,7 +4114,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" spans="1:25" ht="12.75">
+    <row r="132" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4097,7 +4141,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" spans="1:25" ht="12.75">
+    <row r="133" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4124,7 +4168,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" spans="1:25" ht="12.75">
+    <row r="134" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4151,7 +4195,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" spans="1:25" ht="12.75">
+    <row r="135" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4178,7 +4222,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" spans="1:25" ht="12.75">
+    <row r="136" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4205,7 +4249,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" spans="1:25" ht="12.75">
+    <row r="137" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4232,7 +4276,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" spans="1:25" ht="12.75">
+    <row r="138" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4259,7 +4303,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" spans="1:25" ht="12.75">
+    <row r="139" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4286,7 +4330,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" spans="1:25" ht="12.75">
+    <row r="140" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4313,7 +4357,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" spans="1:25" ht="12.75">
+    <row r="141" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4340,7 +4384,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" spans="1:25" ht="12.75">
+    <row r="142" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4367,7 +4411,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" spans="1:25" ht="12.75">
+    <row r="143" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4394,7 +4438,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" spans="1:25" ht="12.75">
+    <row r="144" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4421,7 +4465,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" spans="1:25" ht="12.75">
+    <row r="145" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4448,7 +4492,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" spans="1:25" ht="12.75">
+    <row r="146" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4475,7 +4519,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" spans="1:25" ht="12.75">
+    <row r="147" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4502,7 +4546,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" spans="1:25" ht="12.75">
+    <row r="148" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4529,7 +4573,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" spans="1:25" ht="12.75">
+    <row r="149" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4556,7 +4600,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" spans="1:25" ht="12.75">
+    <row r="150" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4583,7 +4627,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" spans="1:25" ht="12.75">
+    <row r="151" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4610,7 +4654,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" spans="1:25" ht="12.75">
+    <row r="152" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4637,7 +4681,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" spans="1:25" ht="12.75">
+    <row r="153" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4664,7 +4708,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" spans="1:25" ht="12.75">
+    <row r="154" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4691,7 +4735,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" spans="1:25" ht="12.75">
+    <row r="155" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4718,7 +4762,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" spans="1:25" ht="12.75">
+    <row r="156" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4745,7 +4789,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" spans="1:25" ht="12.75">
+    <row r="157" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4772,7 +4816,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" spans="1:25" ht="12.75">
+    <row r="158" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4799,7 +4843,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" spans="1:25" ht="12.75">
+    <row r="159" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4826,7 +4870,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" spans="1:25" ht="12.75">
+    <row r="160" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4853,7 +4897,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" spans="1:25" ht="12.75">
+    <row r="161" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4880,7 +4924,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" spans="1:25" ht="12.75">
+    <row r="162" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4907,7 +4951,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" spans="1:25" ht="12.75">
+    <row r="163" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4934,7 +4978,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" spans="1:25" ht="12.75">
+    <row r="164" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4961,7 +5005,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" spans="1:25" ht="12.75">
+    <row r="165" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4988,7 +5032,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" spans="1:25" ht="12.75">
+    <row r="166" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5015,7 +5059,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" spans="1:25" ht="12.75">
+    <row r="167" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5042,7 +5086,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" spans="1:25" ht="12.75">
+    <row r="168" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5069,7 +5113,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" spans="1:25" ht="12.75">
+    <row r="169" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5096,7 +5140,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" spans="1:25" ht="12.75">
+    <row r="170" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5123,7 +5167,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" spans="1:25" ht="12.75">
+    <row r="171" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5150,7 +5194,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" spans="1:25" ht="12.75">
+    <row r="172" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5177,7 +5221,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" spans="1:25" ht="12.75">
+    <row r="173" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5204,7 +5248,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" spans="1:25" ht="12.75">
+    <row r="174" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5231,7 +5275,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" spans="1:25" ht="12.75">
+    <row r="175" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5258,7 +5302,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" spans="1:25" ht="12.75">
+    <row r="176" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5285,7 +5329,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" spans="1:25" ht="12.75">
+    <row r="177" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5312,7 +5356,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" spans="1:25" ht="12.75">
+    <row r="178" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5339,7 +5383,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" spans="1:25" ht="12.75">
+    <row r="179" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5366,7 +5410,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" spans="1:25" ht="12.75">
+    <row r="180" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5393,7 +5437,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" spans="1:25" ht="12.75">
+    <row r="181" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5420,7 +5464,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" spans="1:25" ht="12.75">
+    <row r="182" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5447,7 +5491,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" spans="1:25" ht="12.75">
+    <row r="183" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5474,7 +5518,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" spans="1:25" ht="12.75">
+    <row r="184" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5501,7 +5545,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" spans="1:25" ht="12.75">
+    <row r="185" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5528,7 +5572,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" spans="1:25" ht="12.75">
+    <row r="186" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5555,7 +5599,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" spans="1:25" ht="12.75">
+    <row r="187" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5582,7 +5626,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" spans="1:25" ht="12.75">
+    <row r="188" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5609,7 +5653,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" spans="1:25" ht="12.75">
+    <row r="189" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5636,7 +5680,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" spans="1:25" ht="12.75">
+    <row r="190" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5663,7 +5707,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" spans="1:25" ht="12.75">
+    <row r="191" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5690,7 +5734,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" spans="1:25" ht="12.75">
+    <row r="192" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5717,7 +5761,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" spans="1:25" ht="12.75">
+    <row r="193" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5744,7 +5788,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" spans="1:25" ht="12.75">
+    <row r="194" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5771,7 +5815,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" spans="1:25" ht="12.75">
+    <row r="195" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5798,7 +5842,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" spans="1:25" ht="12.75">
+    <row r="196" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5825,7 +5869,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" spans="1:25" ht="12.75">
+    <row r="197" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5852,7 +5896,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" spans="1:25" ht="12.75">
+    <row r="198" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5879,7 +5923,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" spans="1:25" ht="12.75">
+    <row r="199" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5906,7 +5950,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" spans="1:25" ht="12.75">
+    <row r="200" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5933,7 +5977,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" spans="1:25" ht="12.75">
+    <row r="201" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5960,7 +6004,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" spans="1:25" ht="12.75">
+    <row r="202" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -5987,7 +6031,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" spans="1:25" ht="12.75">
+    <row r="203" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6014,7 +6058,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" spans="1:25" ht="12.75">
+    <row r="204" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6041,7 +6085,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205" spans="1:25" ht="12.75">
+    <row r="205" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6068,7 +6112,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206" spans="1:25" ht="12.75">
+    <row r="206" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6095,7 +6139,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207" spans="1:25" ht="12.75">
+    <row r="207" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6122,7 +6166,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208" spans="1:25" ht="12.75">
+    <row r="208" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6149,7 +6193,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209" spans="1:25" ht="12.75">
+    <row r="209" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6176,7 +6220,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" spans="1:25" ht="12.75">
+    <row r="210" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6203,7 +6247,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211" spans="1:25" ht="12.75">
+    <row r="211" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6230,7 +6274,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212" spans="1:25" ht="12.75">
+    <row r="212" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6257,7 +6301,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" spans="1:25" ht="12.75">
+    <row r="213" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6284,7 +6328,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214" spans="1:25" ht="12.75">
+    <row r="214" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6311,7 +6355,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215" spans="1:25" ht="12.75">
+    <row r="215" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6338,7 +6382,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216" spans="1:25" ht="12.75">
+    <row r="216" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6365,7 +6409,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217" spans="1:25" ht="12.75">
+    <row r="217" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6392,7 +6436,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218" spans="1:25" ht="12.75">
+    <row r="218" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6419,7 +6463,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219" spans="1:25" ht="12.75">
+    <row r="219" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6446,7 +6490,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220" spans="1:25" ht="12.75">
+    <row r="220" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6473,7 +6517,7 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" spans="1:25" ht="12.75">
+    <row r="221" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6500,7 +6544,7 @@
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
     </row>
-    <row r="222" spans="1:25" ht="12.75">
+    <row r="222" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6527,7 +6571,7 @@
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
     </row>
-    <row r="223" spans="1:25" ht="12.75">
+    <row r="223" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6554,7 +6598,7 @@
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
     </row>
-    <row r="224" spans="1:25" ht="12.75">
+    <row r="224" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6581,7 +6625,7 @@
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
     </row>
-    <row r="225" spans="1:25" ht="12.75">
+    <row r="225" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6608,7 +6652,7 @@
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
     </row>
-    <row r="226" spans="1:25" ht="12.75">
+    <row r="226" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6635,7 +6679,7 @@
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
     </row>
-    <row r="227" spans="1:25" ht="12.75">
+    <row r="227" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6662,7 +6706,7 @@
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
     </row>
-    <row r="228" spans="1:25" ht="12.75">
+    <row r="228" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -6689,7 +6733,7 @@
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
     </row>
-    <row r="229" spans="1:25" ht="12.75">
+    <row r="229" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -6716,7 +6760,7 @@
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
     </row>
-    <row r="230" spans="1:25" ht="12.75">
+    <row r="230" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -6743,7 +6787,7 @@
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
     </row>
-    <row r="231" spans="1:25" ht="12.75">
+    <row r="231" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -6770,7 +6814,7 @@
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232" spans="1:25" ht="12.75">
+    <row r="232" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -6797,7 +6841,7 @@
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
     </row>
-    <row r="233" spans="1:25" ht="12.75">
+    <row r="233" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -6824,7 +6868,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
     </row>
-    <row r="234" spans="1:25" ht="12.75">
+    <row r="234" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6851,7 +6895,7 @@
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
     </row>
-    <row r="235" spans="1:25" ht="12.75">
+    <row r="235" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -6878,7 +6922,7 @@
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
     </row>
-    <row r="236" spans="1:25" ht="12.75">
+    <row r="236" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6905,7 +6949,7 @@
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
     </row>
-    <row r="237" spans="1:25" ht="12.75">
+    <row r="237" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -6932,7 +6976,7 @@
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
     </row>
-    <row r="238" spans="1:25" ht="12.75">
+    <row r="238" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -6959,7 +7003,7 @@
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
     </row>
-    <row r="239" spans="1:25" ht="12.75">
+    <row r="239" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -6986,7 +7030,7 @@
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
     </row>
-    <row r="240" spans="1:25" ht="12.75">
+    <row r="240" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7013,7 +7057,7 @@
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
     </row>
-    <row r="241" spans="1:25" ht="12.75">
+    <row r="241" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7040,7 +7084,7 @@
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
     </row>
-    <row r="242" spans="1:25" ht="12.75">
+    <row r="242" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7067,7 +7111,7 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243" spans="1:25" ht="12.75">
+    <row r="243" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7094,7 +7138,7 @@
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
     </row>
-    <row r="244" spans="1:25" ht="12.75">
+    <row r="244" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -7121,7 +7165,7 @@
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
     </row>
-    <row r="245" spans="1:25" ht="12.75">
+    <row r="245" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -7148,7 +7192,7 @@
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
     </row>
-    <row r="246" spans="1:25" ht="12.75">
+    <row r="246" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -7175,7 +7219,7 @@
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
     </row>
-    <row r="247" spans="1:25" ht="12.75">
+    <row r="247" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -7202,7 +7246,7 @@
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
     </row>
-    <row r="248" spans="1:25" ht="12.75">
+    <row r="248" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -7229,7 +7273,7 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249" spans="1:25" ht="12.75">
+    <row r="249" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -7256,7 +7300,7 @@
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
     </row>
-    <row r="250" spans="1:25" ht="12.75">
+    <row r="250" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -7283,7 +7327,7 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251" spans="1:25" ht="12.75">
+    <row r="251" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -7310,7 +7354,7 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252" spans="1:25" ht="12.75">
+    <row r="252" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -7337,7 +7381,7 @@
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
     </row>
-    <row r="253" spans="1:25" ht="12.75">
+    <row r="253" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -7364,7 +7408,7 @@
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
     </row>
-    <row r="254" spans="1:25" ht="12.75">
+    <row r="254" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -7391,7 +7435,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255" spans="1:25" ht="12.75">
+    <row r="255" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -7418,7 +7462,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256" spans="1:25" ht="12.75">
+    <row r="256" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -7445,7 +7489,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257" spans="1:25" ht="12.75">
+    <row r="257" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -7472,7 +7516,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258" spans="1:25" ht="12.75">
+    <row r="258" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -7499,7 +7543,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" spans="1:25" ht="12.75">
+    <row r="259" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -7526,7 +7570,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" spans="1:25" ht="12.75">
+    <row r="260" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -7553,7 +7597,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" spans="1:25" ht="12.75">
+    <row r="261" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -7580,7 +7624,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" spans="1:25" ht="12.75">
+    <row r="262" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -7607,7 +7651,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" spans="1:25" ht="12.75">
+    <row r="263" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -7634,7 +7678,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264" spans="1:25" ht="12.75">
+    <row r="264" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -7661,7 +7705,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" spans="1:25" ht="12.75">
+    <row r="265" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -7688,7 +7732,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266" spans="1:25" ht="12.75">
+    <row r="266" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -7715,7 +7759,7 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267" spans="1:25" ht="12.75">
+    <row r="267" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -7742,7 +7786,7 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268" spans="1:25" ht="12.75">
+    <row r="268" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -7769,7 +7813,7 @@
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
     </row>
-    <row r="269" spans="1:25" ht="12.75">
+    <row r="269" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -7796,7 +7840,7 @@
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
     </row>
-    <row r="270" spans="1:25" ht="12.75">
+    <row r="270" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -7823,7 +7867,7 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" spans="1:25" ht="12.75">
+    <row r="271" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -7850,7 +7894,7 @@
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
     </row>
-    <row r="272" spans="1:25" ht="12.75">
+    <row r="272" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -7877,7 +7921,7 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273" spans="1:25" ht="12.75">
+    <row r="273" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -7904,7 +7948,7 @@
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
     </row>
-    <row r="274" spans="1:25" ht="12.75">
+    <row r="274" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -7931,7 +7975,7 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" spans="1:25" ht="12.75">
+    <row r="275" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -7958,7 +8002,7 @@
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
     </row>
-    <row r="276" spans="1:25" ht="12.75">
+    <row r="276" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -7985,7 +8029,7 @@
       <c r="X276" s="1"/>
       <c r="Y276" s="1"/>
     </row>
-    <row r="277" spans="1:25" ht="12.75">
+    <row r="277" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -8012,7 +8056,7 @@
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
     </row>
-    <row r="278" spans="1:25" ht="12.75">
+    <row r="278" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -8039,7 +8083,7 @@
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
     </row>
-    <row r="279" spans="1:25" ht="12.75">
+    <row r="279" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -8066,7 +8110,7 @@
       <c r="X279" s="1"/>
       <c r="Y279" s="1"/>
     </row>
-    <row r="280" spans="1:25" ht="12.75">
+    <row r="280" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -8093,7 +8137,7 @@
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
     </row>
-    <row r="281" spans="1:25" ht="12.75">
+    <row r="281" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -8120,7 +8164,7 @@
       <c r="X281" s="1"/>
       <c r="Y281" s="1"/>
     </row>
-    <row r="282" spans="1:25" ht="12.75">
+    <row r="282" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -8147,7 +8191,7 @@
       <c r="X282" s="1"/>
       <c r="Y282" s="1"/>
     </row>
-    <row r="283" spans="1:25" ht="12.75">
+    <row r="283" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -8174,7 +8218,7 @@
       <c r="X283" s="1"/>
       <c r="Y283" s="1"/>
     </row>
-    <row r="284" spans="1:25" ht="12.75">
+    <row r="284" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -8201,7 +8245,7 @@
       <c r="X284" s="1"/>
       <c r="Y284" s="1"/>
     </row>
-    <row r="285" spans="1:25" ht="12.75">
+    <row r="285" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -8228,7 +8272,7 @@
       <c r="X285" s="1"/>
       <c r="Y285" s="1"/>
     </row>
-    <row r="286" spans="1:25" ht="12.75">
+    <row r="286" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -8255,7 +8299,7 @@
       <c r="X286" s="1"/>
       <c r="Y286" s="1"/>
     </row>
-    <row r="287" spans="1:25" ht="12.75">
+    <row r="287" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -8282,7 +8326,7 @@
       <c r="X287" s="1"/>
       <c r="Y287" s="1"/>
     </row>
-    <row r="288" spans="1:25" ht="12.75">
+    <row r="288" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -8309,7 +8353,7 @@
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
     </row>
-    <row r="289" spans="1:25" ht="12.75">
+    <row r="289" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -8336,7 +8380,7 @@
       <c r="X289" s="1"/>
       <c r="Y289" s="1"/>
     </row>
-    <row r="290" spans="1:25" ht="12.75">
+    <row r="290" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -8363,7 +8407,7 @@
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
     </row>
-    <row r="291" spans="1:25" ht="12.75">
+    <row r="291" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -8390,7 +8434,7 @@
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
     </row>
-    <row r="292" spans="1:25" ht="12.75">
+    <row r="292" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -8417,7 +8461,7 @@
       <c r="X292" s="1"/>
       <c r="Y292" s="1"/>
     </row>
-    <row r="293" spans="1:25" ht="12.75">
+    <row r="293" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -8444,7 +8488,7 @@
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
     </row>
-    <row r="294" spans="1:25" ht="12.75">
+    <row r="294" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -8471,7 +8515,7 @@
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
     </row>
-    <row r="295" spans="1:25" ht="12.75">
+    <row r="295" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -8498,7 +8542,7 @@
       <c r="X295" s="1"/>
       <c r="Y295" s="1"/>
     </row>
-    <row r="296" spans="1:25" ht="12.75">
+    <row r="296" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -8525,7 +8569,7 @@
       <c r="X296" s="1"/>
       <c r="Y296" s="1"/>
     </row>
-    <row r="297" spans="1:25" ht="12.75">
+    <row r="297" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -8552,7 +8596,7 @@
       <c r="X297" s="1"/>
       <c r="Y297" s="1"/>
     </row>
-    <row r="298" spans="1:25" ht="12.75">
+    <row r="298" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -8579,7 +8623,7 @@
       <c r="X298" s="1"/>
       <c r="Y298" s="1"/>
     </row>
-    <row r="299" spans="1:25" ht="12.75">
+    <row r="299" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -8606,7 +8650,7 @@
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
     </row>
-    <row r="300" spans="1:25" ht="12.75">
+    <row r="300" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -8633,7 +8677,7 @@
       <c r="X300" s="1"/>
       <c r="Y300" s="1"/>
     </row>
-    <row r="301" spans="1:25" ht="12.75">
+    <row r="301" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -8660,7 +8704,7 @@
       <c r="X301" s="1"/>
       <c r="Y301" s="1"/>
     </row>
-    <row r="302" spans="1:25" ht="12.75">
+    <row r="302" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -8687,7 +8731,7 @@
       <c r="X302" s="1"/>
       <c r="Y302" s="1"/>
     </row>
-    <row r="303" spans="1:25" ht="12.75">
+    <row r="303" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -8714,7 +8758,7 @@
       <c r="X303" s="1"/>
       <c r="Y303" s="1"/>
     </row>
-    <row r="304" spans="1:25" ht="12.75">
+    <row r="304" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -8741,7 +8785,7 @@
       <c r="X304" s="1"/>
       <c r="Y304" s="1"/>
     </row>
-    <row r="305" spans="1:25" ht="12.75">
+    <row r="305" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -8768,7 +8812,7 @@
       <c r="X305" s="1"/>
       <c r="Y305" s="1"/>
     </row>
-    <row r="306" spans="1:25" ht="12.75">
+    <row r="306" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -8795,7 +8839,7 @@
       <c r="X306" s="1"/>
       <c r="Y306" s="1"/>
     </row>
-    <row r="307" spans="1:25" ht="12.75">
+    <row r="307" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -8822,7 +8866,7 @@
       <c r="X307" s="1"/>
       <c r="Y307" s="1"/>
     </row>
-    <row r="308" spans="1:25" ht="12.75">
+    <row r="308" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -8849,7 +8893,7 @@
       <c r="X308" s="1"/>
       <c r="Y308" s="1"/>
     </row>
-    <row r="309" spans="1:25" ht="12.75">
+    <row r="309" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -8876,7 +8920,7 @@
       <c r="X309" s="1"/>
       <c r="Y309" s="1"/>
     </row>
-    <row r="310" spans="1:25" ht="12.75">
+    <row r="310" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -8903,7 +8947,7 @@
       <c r="X310" s="1"/>
       <c r="Y310" s="1"/>
     </row>
-    <row r="311" spans="1:25" ht="12.75">
+    <row r="311" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -8930,7 +8974,7 @@
       <c r="X311" s="1"/>
       <c r="Y311" s="1"/>
     </row>
-    <row r="312" spans="1:25" ht="12.75">
+    <row r="312" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -8957,7 +9001,7 @@
       <c r="X312" s="1"/>
       <c r="Y312" s="1"/>
     </row>
-    <row r="313" spans="1:25" ht="12.75">
+    <row r="313" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -8984,7 +9028,7 @@
       <c r="X313" s="1"/>
       <c r="Y313" s="1"/>
     </row>
-    <row r="314" spans="1:25" ht="12.75">
+    <row r="314" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -9011,7 +9055,7 @@
       <c r="X314" s="1"/>
       <c r="Y314" s="1"/>
     </row>
-    <row r="315" spans="1:25" ht="12.75">
+    <row r="315" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -9038,7 +9082,7 @@
       <c r="X315" s="1"/>
       <c r="Y315" s="1"/>
     </row>
-    <row r="316" spans="1:25" ht="12.75">
+    <row r="316" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -9065,7 +9109,7 @@
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
     </row>
-    <row r="317" spans="1:25" ht="12.75">
+    <row r="317" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -9092,7 +9136,7 @@
       <c r="X317" s="1"/>
       <c r="Y317" s="1"/>
     </row>
-    <row r="318" spans="1:25" ht="12.75">
+    <row r="318" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -9119,7 +9163,7 @@
       <c r="X318" s="1"/>
       <c r="Y318" s="1"/>
     </row>
-    <row r="319" spans="1:25" ht="12.75">
+    <row r="319" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -9146,7 +9190,7 @@
       <c r="X319" s="1"/>
       <c r="Y319" s="1"/>
     </row>
-    <row r="320" spans="1:25" ht="12.75">
+    <row r="320" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -9173,7 +9217,7 @@
       <c r="X320" s="1"/>
       <c r="Y320" s="1"/>
     </row>
-    <row r="321" spans="1:25" ht="12.75">
+    <row r="321" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -9200,7 +9244,7 @@
       <c r="X321" s="1"/>
       <c r="Y321" s="1"/>
     </row>
-    <row r="322" spans="1:25" ht="12.75">
+    <row r="322" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -9227,7 +9271,7 @@
       <c r="X322" s="1"/>
       <c r="Y322" s="1"/>
     </row>
-    <row r="323" spans="1:25" ht="12.75">
+    <row r="323" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -9254,7 +9298,7 @@
       <c r="X323" s="1"/>
       <c r="Y323" s="1"/>
     </row>
-    <row r="324" spans="1:25" ht="12.75">
+    <row r="324" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -9281,7 +9325,7 @@
       <c r="X324" s="1"/>
       <c r="Y324" s="1"/>
     </row>
-    <row r="325" spans="1:25" ht="12.75">
+    <row r="325" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -9308,7 +9352,7 @@
       <c r="X325" s="1"/>
       <c r="Y325" s="1"/>
     </row>
-    <row r="326" spans="1:25" ht="12.75">
+    <row r="326" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -9335,7 +9379,7 @@
       <c r="X326" s="1"/>
       <c r="Y326" s="1"/>
     </row>
-    <row r="327" spans="1:25" ht="12.75">
+    <row r="327" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -9362,7 +9406,7 @@
       <c r="X327" s="1"/>
       <c r="Y327" s="1"/>
     </row>
-    <row r="328" spans="1:25" ht="12.75">
+    <row r="328" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -9389,7 +9433,7 @@
       <c r="X328" s="1"/>
       <c r="Y328" s="1"/>
     </row>
-    <row r="329" spans="1:25" ht="12.75">
+    <row r="329" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -9416,7 +9460,7 @@
       <c r="X329" s="1"/>
       <c r="Y329" s="1"/>
     </row>
-    <row r="330" spans="1:25" ht="12.75">
+    <row r="330" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -9443,7 +9487,7 @@
       <c r="X330" s="1"/>
       <c r="Y330" s="1"/>
     </row>
-    <row r="331" spans="1:25" ht="12.75">
+    <row r="331" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -9470,7 +9514,7 @@
       <c r="X331" s="1"/>
       <c r="Y331" s="1"/>
     </row>
-    <row r="332" spans="1:25" ht="12.75">
+    <row r="332" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -9497,7 +9541,7 @@
       <c r="X332" s="1"/>
       <c r="Y332" s="1"/>
     </row>
-    <row r="333" spans="1:25" ht="12.75">
+    <row r="333" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -9524,7 +9568,7 @@
       <c r="X333" s="1"/>
       <c r="Y333" s="1"/>
     </row>
-    <row r="334" spans="1:25" ht="12.75">
+    <row r="334" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -9551,7 +9595,7 @@
       <c r="X334" s="1"/>
       <c r="Y334" s="1"/>
     </row>
-    <row r="335" spans="1:25" ht="12.75">
+    <row r="335" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -9578,7 +9622,7 @@
       <c r="X335" s="1"/>
       <c r="Y335" s="1"/>
     </row>
-    <row r="336" spans="1:25" ht="12.75">
+    <row r="336" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -9605,7 +9649,7 @@
       <c r="X336" s="1"/>
       <c r="Y336" s="1"/>
     </row>
-    <row r="337" spans="1:25" ht="12.75">
+    <row r="337" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -9632,7 +9676,7 @@
       <c r="X337" s="1"/>
       <c r="Y337" s="1"/>
     </row>
-    <row r="338" spans="1:25" ht="12.75">
+    <row r="338" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -9659,7 +9703,7 @@
       <c r="X338" s="1"/>
       <c r="Y338" s="1"/>
     </row>
-    <row r="339" spans="1:25" ht="12.75">
+    <row r="339" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -9686,7 +9730,7 @@
       <c r="X339" s="1"/>
       <c r="Y339" s="1"/>
     </row>
-    <row r="340" spans="1:25" ht="12.75">
+    <row r="340" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -9713,7 +9757,7 @@
       <c r="X340" s="1"/>
       <c r="Y340" s="1"/>
     </row>
-    <row r="341" spans="1:25" ht="12.75">
+    <row r="341" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -9740,7 +9784,7 @@
       <c r="X341" s="1"/>
       <c r="Y341" s="1"/>
     </row>
-    <row r="342" spans="1:25" ht="12.75">
+    <row r="342" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -9767,7 +9811,7 @@
       <c r="X342" s="1"/>
       <c r="Y342" s="1"/>
     </row>
-    <row r="343" spans="1:25" ht="12.75">
+    <row r="343" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -9794,7 +9838,7 @@
       <c r="X343" s="1"/>
       <c r="Y343" s="1"/>
     </row>
-    <row r="344" spans="1:25" ht="12.75">
+    <row r="344" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -9821,7 +9865,7 @@
       <c r="X344" s="1"/>
       <c r="Y344" s="1"/>
     </row>
-    <row r="345" spans="1:25" ht="12.75">
+    <row r="345" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -9848,7 +9892,7 @@
       <c r="X345" s="1"/>
       <c r="Y345" s="1"/>
     </row>
-    <row r="346" spans="1:25" ht="12.75">
+    <row r="346" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -9875,7 +9919,7 @@
       <c r="X346" s="1"/>
       <c r="Y346" s="1"/>
     </row>
-    <row r="347" spans="1:25" ht="12.75">
+    <row r="347" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -9902,7 +9946,7 @@
       <c r="X347" s="1"/>
       <c r="Y347" s="1"/>
     </row>
-    <row r="348" spans="1:25" ht="12.75">
+    <row r="348" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -9929,7 +9973,7 @@
       <c r="X348" s="1"/>
       <c r="Y348" s="1"/>
     </row>
-    <row r="349" spans="1:25" ht="12.75">
+    <row r="349" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -9956,7 +10000,7 @@
       <c r="X349" s="1"/>
       <c r="Y349" s="1"/>
     </row>
-    <row r="350" spans="1:25" ht="12.75">
+    <row r="350" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -9983,7 +10027,7 @@
       <c r="X350" s="1"/>
       <c r="Y350" s="1"/>
     </row>
-    <row r="351" spans="1:25" ht="12.75">
+    <row r="351" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -10010,7 +10054,7 @@
       <c r="X351" s="1"/>
       <c r="Y351" s="1"/>
     </row>
-    <row r="352" spans="1:25" ht="12.75">
+    <row r="352" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -10037,7 +10081,7 @@
       <c r="X352" s="1"/>
       <c r="Y352" s="1"/>
     </row>
-    <row r="353" spans="1:25" ht="12.75">
+    <row r="353" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -10064,7 +10108,7 @@
       <c r="X353" s="1"/>
       <c r="Y353" s="1"/>
     </row>
-    <row r="354" spans="1:25" ht="12.75">
+    <row r="354" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -10091,7 +10135,7 @@
       <c r="X354" s="1"/>
       <c r="Y354" s="1"/>
     </row>
-    <row r="355" spans="1:25" ht="12.75">
+    <row r="355" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -10118,7 +10162,7 @@
       <c r="X355" s="1"/>
       <c r="Y355" s="1"/>
     </row>
-    <row r="356" spans="1:25" ht="12.75">
+    <row r="356" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -10145,7 +10189,7 @@
       <c r="X356" s="1"/>
       <c r="Y356" s="1"/>
     </row>
-    <row r="357" spans="1:25" ht="12.75">
+    <row r="357" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -10172,7 +10216,7 @@
       <c r="X357" s="1"/>
       <c r="Y357" s="1"/>
     </row>
-    <row r="358" spans="1:25" ht="12.75">
+    <row r="358" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -10199,7 +10243,7 @@
       <c r="X358" s="1"/>
       <c r="Y358" s="1"/>
     </row>
-    <row r="359" spans="1:25" ht="12.75">
+    <row r="359" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -10226,7 +10270,7 @@
       <c r="X359" s="1"/>
       <c r="Y359" s="1"/>
     </row>
-    <row r="360" spans="1:25" ht="12.75">
+    <row r="360" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -10253,7 +10297,7 @@
       <c r="X360" s="1"/>
       <c r="Y360" s="1"/>
     </row>
-    <row r="361" spans="1:25" ht="12.75">
+    <row r="361" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -10280,7 +10324,7 @@
       <c r="X361" s="1"/>
       <c r="Y361" s="1"/>
     </row>
-    <row r="362" spans="1:25" ht="12.75">
+    <row r="362" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -10307,7 +10351,7 @@
       <c r="X362" s="1"/>
       <c r="Y362" s="1"/>
     </row>
-    <row r="363" spans="1:25" ht="12.75">
+    <row r="363" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -10334,7 +10378,7 @@
       <c r="X363" s="1"/>
       <c r="Y363" s="1"/>
     </row>
-    <row r="364" spans="1:25" ht="12.75">
+    <row r="364" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -10361,7 +10405,7 @@
       <c r="X364" s="1"/>
       <c r="Y364" s="1"/>
     </row>
-    <row r="365" spans="1:25" ht="12.75">
+    <row r="365" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -10388,7 +10432,7 @@
       <c r="X365" s="1"/>
       <c r="Y365" s="1"/>
     </row>
-    <row r="366" spans="1:25" ht="12.75">
+    <row r="366" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -10415,7 +10459,7 @@
       <c r="X366" s="1"/>
       <c r="Y366" s="1"/>
     </row>
-    <row r="367" spans="1:25" ht="12.75">
+    <row r="367" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -10442,7 +10486,7 @@
       <c r="X367" s="1"/>
       <c r="Y367" s="1"/>
     </row>
-    <row r="368" spans="1:25" ht="12.75">
+    <row r="368" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -10469,7 +10513,7 @@
       <c r="X368" s="1"/>
       <c r="Y368" s="1"/>
     </row>
-    <row r="369" spans="1:25" ht="12.75">
+    <row r="369" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -10496,7 +10540,7 @@
       <c r="X369" s="1"/>
       <c r="Y369" s="1"/>
     </row>
-    <row r="370" spans="1:25" ht="12.75">
+    <row r="370" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -10523,7 +10567,7 @@
       <c r="X370" s="1"/>
       <c r="Y370" s="1"/>
     </row>
-    <row r="371" spans="1:25" ht="12.75">
+    <row r="371" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -10550,7 +10594,7 @@
       <c r="X371" s="1"/>
       <c r="Y371" s="1"/>
     </row>
-    <row r="372" spans="1:25" ht="12.75">
+    <row r="372" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -10577,7 +10621,7 @@
       <c r="X372" s="1"/>
       <c r="Y372" s="1"/>
     </row>
-    <row r="373" spans="1:25" ht="12.75">
+    <row r="373" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -10604,7 +10648,7 @@
       <c r="X373" s="1"/>
       <c r="Y373" s="1"/>
     </row>
-    <row r="374" spans="1:25" ht="12.75">
+    <row r="374" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -10631,7 +10675,7 @@
       <c r="X374" s="1"/>
       <c r="Y374" s="1"/>
     </row>
-    <row r="375" spans="1:25" ht="12.75">
+    <row r="375" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -10658,7 +10702,7 @@
       <c r="X375" s="1"/>
       <c r="Y375" s="1"/>
     </row>
-    <row r="376" spans="1:25" ht="12.75">
+    <row r="376" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -10685,7 +10729,7 @@
       <c r="X376" s="1"/>
       <c r="Y376" s="1"/>
     </row>
-    <row r="377" spans="1:25" ht="12.75">
+    <row r="377" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -10712,7 +10756,7 @@
       <c r="X377" s="1"/>
       <c r="Y377" s="1"/>
     </row>
-    <row r="378" spans="1:25" ht="12.75">
+    <row r="378" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -10739,7 +10783,7 @@
       <c r="X378" s="1"/>
       <c r="Y378" s="1"/>
     </row>
-    <row r="379" spans="1:25" ht="12.75">
+    <row r="379" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -10766,7 +10810,7 @@
       <c r="X379" s="1"/>
       <c r="Y379" s="1"/>
     </row>
-    <row r="380" spans="1:25" ht="12.75">
+    <row r="380" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -10793,7 +10837,7 @@
       <c r="X380" s="1"/>
       <c r="Y380" s="1"/>
     </row>
-    <row r="381" spans="1:25" ht="12.75">
+    <row r="381" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -10820,7 +10864,7 @@
       <c r="X381" s="1"/>
       <c r="Y381" s="1"/>
     </row>
-    <row r="382" spans="1:25" ht="12.75">
+    <row r="382" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -10847,7 +10891,7 @@
       <c r="X382" s="1"/>
       <c r="Y382" s="1"/>
     </row>
-    <row r="383" spans="1:25" ht="12.75">
+    <row r="383" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -10874,7 +10918,7 @@
       <c r="X383" s="1"/>
       <c r="Y383" s="1"/>
     </row>
-    <row r="384" spans="1:25" ht="12.75">
+    <row r="384" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -10901,7 +10945,7 @@
       <c r="X384" s="1"/>
       <c r="Y384" s="1"/>
     </row>
-    <row r="385" spans="1:25" ht="12.75">
+    <row r="385" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -10928,7 +10972,7 @@
       <c r="X385" s="1"/>
       <c r="Y385" s="1"/>
     </row>
-    <row r="386" spans="1:25" ht="12.75">
+    <row r="386" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -10955,7 +10999,7 @@
       <c r="X386" s="1"/>
       <c r="Y386" s="1"/>
     </row>
-    <row r="387" spans="1:25" ht="12.75">
+    <row r="387" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -10982,7 +11026,7 @@
       <c r="X387" s="1"/>
       <c r="Y387" s="1"/>
     </row>
-    <row r="388" spans="1:25" ht="12.75">
+    <row r="388" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -11009,7 +11053,7 @@
       <c r="X388" s="1"/>
       <c r="Y388" s="1"/>
     </row>
-    <row r="389" spans="1:25" ht="12.75">
+    <row r="389" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -11036,7 +11080,7 @@
       <c r="X389" s="1"/>
       <c r="Y389" s="1"/>
     </row>
-    <row r="390" spans="1:25" ht="12.75">
+    <row r="390" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -11063,7 +11107,7 @@
       <c r="X390" s="1"/>
       <c r="Y390" s="1"/>
     </row>
-    <row r="391" spans="1:25" ht="12.75">
+    <row r="391" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -11090,7 +11134,7 @@
       <c r="X391" s="1"/>
       <c r="Y391" s="1"/>
     </row>
-    <row r="392" spans="1:25" ht="12.75">
+    <row r="392" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -11117,7 +11161,7 @@
       <c r="X392" s="1"/>
       <c r="Y392" s="1"/>
     </row>
-    <row r="393" spans="1:25" ht="12.75">
+    <row r="393" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -11144,7 +11188,7 @@
       <c r="X393" s="1"/>
       <c r="Y393" s="1"/>
     </row>
-    <row r="394" spans="1:25" ht="12.75">
+    <row r="394" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -11171,7 +11215,7 @@
       <c r="X394" s="1"/>
       <c r="Y394" s="1"/>
     </row>
-    <row r="395" spans="1:25" ht="12.75">
+    <row r="395" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -11198,7 +11242,7 @@
       <c r="X395" s="1"/>
       <c r="Y395" s="1"/>
     </row>
-    <row r="396" spans="1:25" ht="12.75">
+    <row r="396" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -11225,7 +11269,7 @@
       <c r="X396" s="1"/>
       <c r="Y396" s="1"/>
     </row>
-    <row r="397" spans="1:25" ht="12.75">
+    <row r="397" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -11252,7 +11296,7 @@
       <c r="X397" s="1"/>
       <c r="Y397" s="1"/>
     </row>
-    <row r="398" spans="1:25" ht="12.75">
+    <row r="398" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -11279,7 +11323,7 @@
       <c r="X398" s="1"/>
       <c r="Y398" s="1"/>
     </row>
-    <row r="399" spans="1:25" ht="12.75">
+    <row r="399" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -11306,7 +11350,7 @@
       <c r="X399" s="1"/>
       <c r="Y399" s="1"/>
     </row>
-    <row r="400" spans="1:25" ht="12.75">
+    <row r="400" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -11333,7 +11377,7 @@
       <c r="X400" s="1"/>
       <c r="Y400" s="1"/>
     </row>
-    <row r="401" spans="1:25" ht="12.75">
+    <row r="401" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -11360,7 +11404,7 @@
       <c r="X401" s="1"/>
       <c r="Y401" s="1"/>
     </row>
-    <row r="402" spans="1:25" ht="12.75">
+    <row r="402" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -11387,7 +11431,7 @@
       <c r="X402" s="1"/>
       <c r="Y402" s="1"/>
     </row>
-    <row r="403" spans="1:25" ht="12.75">
+    <row r="403" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -11414,7 +11458,7 @@
       <c r="X403" s="1"/>
       <c r="Y403" s="1"/>
     </row>
-    <row r="404" spans="1:25" ht="12.75">
+    <row r="404" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -11441,7 +11485,7 @@
       <c r="X404" s="1"/>
       <c r="Y404" s="1"/>
     </row>
-    <row r="405" spans="1:25" ht="12.75">
+    <row r="405" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -11468,7 +11512,7 @@
       <c r="X405" s="1"/>
       <c r="Y405" s="1"/>
     </row>
-    <row r="406" spans="1:25" ht="12.75">
+    <row r="406" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -11495,7 +11539,7 @@
       <c r="X406" s="1"/>
       <c r="Y406" s="1"/>
     </row>
-    <row r="407" spans="1:25" ht="12.75">
+    <row r="407" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -11522,7 +11566,7 @@
       <c r="X407" s="1"/>
       <c r="Y407" s="1"/>
     </row>
-    <row r="408" spans="1:25" ht="12.75">
+    <row r="408" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -11549,7 +11593,7 @@
       <c r="X408" s="1"/>
       <c r="Y408" s="1"/>
     </row>
-    <row r="409" spans="1:25" ht="12.75">
+    <row r="409" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -11576,7 +11620,7 @@
       <c r="X409" s="1"/>
       <c r="Y409" s="1"/>
     </row>
-    <row r="410" spans="1:25" ht="12.75">
+    <row r="410" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -11603,7 +11647,7 @@
       <c r="X410" s="1"/>
       <c r="Y410" s="1"/>
     </row>
-    <row r="411" spans="1:25" ht="12.75">
+    <row r="411" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -11630,7 +11674,7 @@
       <c r="X411" s="1"/>
       <c r="Y411" s="1"/>
     </row>
-    <row r="412" spans="1:25" ht="12.75">
+    <row r="412" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -11657,7 +11701,7 @@
       <c r="X412" s="1"/>
       <c r="Y412" s="1"/>
     </row>
-    <row r="413" spans="1:25" ht="12.75">
+    <row r="413" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -11684,7 +11728,7 @@
       <c r="X413" s="1"/>
       <c r="Y413" s="1"/>
     </row>
-    <row r="414" spans="1:25" ht="12.75">
+    <row r="414" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -11711,7 +11755,7 @@
       <c r="X414" s="1"/>
       <c r="Y414" s="1"/>
     </row>
-    <row r="415" spans="1:25" ht="12.75">
+    <row r="415" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -11738,7 +11782,7 @@
       <c r="X415" s="1"/>
       <c r="Y415" s="1"/>
     </row>
-    <row r="416" spans="1:25" ht="12.75">
+    <row r="416" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -11765,7 +11809,7 @@
       <c r="X416" s="1"/>
       <c r="Y416" s="1"/>
     </row>
-    <row r="417" spans="1:25" ht="12.75">
+    <row r="417" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -11792,7 +11836,7 @@
       <c r="X417" s="1"/>
       <c r="Y417" s="1"/>
     </row>
-    <row r="418" spans="1:25" ht="12.75">
+    <row r="418" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -11819,7 +11863,7 @@
       <c r="X418" s="1"/>
       <c r="Y418" s="1"/>
     </row>
-    <row r="419" spans="1:25" ht="12.75">
+    <row r="419" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -11846,7 +11890,7 @@
       <c r="X419" s="1"/>
       <c r="Y419" s="1"/>
     </row>
-    <row r="420" spans="1:25" ht="12.75">
+    <row r="420" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -11873,7 +11917,7 @@
       <c r="X420" s="1"/>
       <c r="Y420" s="1"/>
     </row>
-    <row r="421" spans="1:25" ht="12.75">
+    <row r="421" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -11900,7 +11944,7 @@
       <c r="X421" s="1"/>
       <c r="Y421" s="1"/>
     </row>
-    <row r="422" spans="1:25" ht="12.75">
+    <row r="422" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -11927,7 +11971,7 @@
       <c r="X422" s="1"/>
       <c r="Y422" s="1"/>
     </row>
-    <row r="423" spans="1:25" ht="12.75">
+    <row r="423" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -11954,7 +11998,7 @@
       <c r="X423" s="1"/>
       <c r="Y423" s="1"/>
     </row>
-    <row r="424" spans="1:25" ht="12.75">
+    <row r="424" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -11981,7 +12025,7 @@
       <c r="X424" s="1"/>
       <c r="Y424" s="1"/>
     </row>
-    <row r="425" spans="1:25" ht="12.75">
+    <row r="425" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -12008,7 +12052,7 @@
       <c r="X425" s="1"/>
       <c r="Y425" s="1"/>
     </row>
-    <row r="426" spans="1:25" ht="12.75">
+    <row r="426" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -12035,7 +12079,7 @@
       <c r="X426" s="1"/>
       <c r="Y426" s="1"/>
     </row>
-    <row r="427" spans="1:25" ht="12.75">
+    <row r="427" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -12062,7 +12106,7 @@
       <c r="X427" s="1"/>
       <c r="Y427" s="1"/>
     </row>
-    <row r="428" spans="1:25" ht="12.75">
+    <row r="428" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -12089,7 +12133,7 @@
       <c r="X428" s="1"/>
       <c r="Y428" s="1"/>
     </row>
-    <row r="429" spans="1:25" ht="12.75">
+    <row r="429" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -12116,7 +12160,7 @@
       <c r="X429" s="1"/>
       <c r="Y429" s="1"/>
     </row>
-    <row r="430" spans="1:25" ht="12.75">
+    <row r="430" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -12143,7 +12187,7 @@
       <c r="X430" s="1"/>
       <c r="Y430" s="1"/>
     </row>
-    <row r="431" spans="1:25" ht="12.75">
+    <row r="431" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -12170,7 +12214,7 @@
       <c r="X431" s="1"/>
       <c r="Y431" s="1"/>
     </row>
-    <row r="432" spans="1:25" ht="12.75">
+    <row r="432" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -12197,7 +12241,7 @@
       <c r="X432" s="1"/>
       <c r="Y432" s="1"/>
     </row>
-    <row r="433" spans="1:25" ht="12.75">
+    <row r="433" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -12224,7 +12268,7 @@
       <c r="X433" s="1"/>
       <c r="Y433" s="1"/>
     </row>
-    <row r="434" spans="1:25" ht="12.75">
+    <row r="434" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -12251,7 +12295,7 @@
       <c r="X434" s="1"/>
       <c r="Y434" s="1"/>
     </row>
-    <row r="435" spans="1:25" ht="12.75">
+    <row r="435" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -12278,7 +12322,7 @@
       <c r="X435" s="1"/>
       <c r="Y435" s="1"/>
     </row>
-    <row r="436" spans="1:25" ht="12.75">
+    <row r="436" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -12305,7 +12349,7 @@
       <c r="X436" s="1"/>
       <c r="Y436" s="1"/>
     </row>
-    <row r="437" spans="1:25" ht="12.75">
+    <row r="437" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -12332,7 +12376,7 @@
       <c r="X437" s="1"/>
       <c r="Y437" s="1"/>
     </row>
-    <row r="438" spans="1:25" ht="12.75">
+    <row r="438" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -12359,7 +12403,7 @@
       <c r="X438" s="1"/>
       <c r="Y438" s="1"/>
     </row>
-    <row r="439" spans="1:25" ht="12.75">
+    <row r="439" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -12386,7 +12430,7 @@
       <c r="X439" s="1"/>
       <c r="Y439" s="1"/>
     </row>
-    <row r="440" spans="1:25" ht="12.75">
+    <row r="440" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -12413,7 +12457,7 @@
       <c r="X440" s="1"/>
       <c r="Y440" s="1"/>
     </row>
-    <row r="441" spans="1:25" ht="12.75">
+    <row r="441" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -12440,7 +12484,7 @@
       <c r="X441" s="1"/>
       <c r="Y441" s="1"/>
     </row>
-    <row r="442" spans="1:25" ht="12.75">
+    <row r="442" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -12467,7 +12511,7 @@
       <c r="X442" s="1"/>
       <c r="Y442" s="1"/>
     </row>
-    <row r="443" spans="1:25" ht="12.75">
+    <row r="443" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -12494,7 +12538,7 @@
       <c r="X443" s="1"/>
       <c r="Y443" s="1"/>
     </row>
-    <row r="444" spans="1:25" ht="12.75">
+    <row r="444" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -12521,7 +12565,7 @@
       <c r="X444" s="1"/>
       <c r="Y444" s="1"/>
     </row>
-    <row r="445" spans="1:25" ht="12.75">
+    <row r="445" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -12548,7 +12592,7 @@
       <c r="X445" s="1"/>
       <c r="Y445" s="1"/>
     </row>
-    <row r="446" spans="1:25" ht="12.75">
+    <row r="446" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -12575,7 +12619,7 @@
       <c r="X446" s="1"/>
       <c r="Y446" s="1"/>
     </row>
-    <row r="447" spans="1:25" ht="12.75">
+    <row r="447" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -12602,7 +12646,7 @@
       <c r="X447" s="1"/>
       <c r="Y447" s="1"/>
     </row>
-    <row r="448" spans="1:25" ht="12.75">
+    <row r="448" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -12629,7 +12673,7 @@
       <c r="X448" s="1"/>
       <c r="Y448" s="1"/>
     </row>
-    <row r="449" spans="1:25" ht="12.75">
+    <row r="449" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -12656,7 +12700,7 @@
       <c r="X449" s="1"/>
       <c r="Y449" s="1"/>
     </row>
-    <row r="450" spans="1:25" ht="12.75">
+    <row r="450" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -12683,7 +12727,7 @@
       <c r="X450" s="1"/>
       <c r="Y450" s="1"/>
     </row>
-    <row r="451" spans="1:25" ht="12.75">
+    <row r="451" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -12710,7 +12754,7 @@
       <c r="X451" s="1"/>
       <c r="Y451" s="1"/>
     </row>
-    <row r="452" spans="1:25" ht="12.75">
+    <row r="452" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -12737,7 +12781,7 @@
       <c r="X452" s="1"/>
       <c r="Y452" s="1"/>
     </row>
-    <row r="453" spans="1:25" ht="12.75">
+    <row r="453" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -12764,7 +12808,7 @@
       <c r="X453" s="1"/>
       <c r="Y453" s="1"/>
     </row>
-    <row r="454" spans="1:25" ht="12.75">
+    <row r="454" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -12791,7 +12835,7 @@
       <c r="X454" s="1"/>
       <c r="Y454" s="1"/>
     </row>
-    <row r="455" spans="1:25" ht="12.75">
+    <row r="455" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -12818,7 +12862,7 @@
       <c r="X455" s="1"/>
       <c r="Y455" s="1"/>
     </row>
-    <row r="456" spans="1:25" ht="12.75">
+    <row r="456" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -12845,7 +12889,7 @@
       <c r="X456" s="1"/>
       <c r="Y456" s="1"/>
     </row>
-    <row r="457" spans="1:25" ht="12.75">
+    <row r="457" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -12872,7 +12916,7 @@
       <c r="X457" s="1"/>
       <c r="Y457" s="1"/>
     </row>
-    <row r="458" spans="1:25" ht="12.75">
+    <row r="458" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -12899,7 +12943,7 @@
       <c r="X458" s="1"/>
       <c r="Y458" s="1"/>
     </row>
-    <row r="459" spans="1:25" ht="12.75">
+    <row r="459" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -12926,7 +12970,7 @@
       <c r="X459" s="1"/>
       <c r="Y459" s="1"/>
     </row>
-    <row r="460" spans="1:25" ht="12.75">
+    <row r="460" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -12953,7 +12997,7 @@
       <c r="X460" s="1"/>
       <c r="Y460" s="1"/>
     </row>
-    <row r="461" spans="1:25" ht="12.75">
+    <row r="461" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -12980,7 +13024,7 @@
       <c r="X461" s="1"/>
       <c r="Y461" s="1"/>
     </row>
-    <row r="462" spans="1:25" ht="12.75">
+    <row r="462" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -13007,7 +13051,7 @@
       <c r="X462" s="1"/>
       <c r="Y462" s="1"/>
     </row>
-    <row r="463" spans="1:25" ht="12.75">
+    <row r="463" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -13034,7 +13078,7 @@
       <c r="X463" s="1"/>
       <c r="Y463" s="1"/>
     </row>
-    <row r="464" spans="1:25" ht="12.75">
+    <row r="464" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -13061,7 +13105,7 @@
       <c r="X464" s="1"/>
       <c r="Y464" s="1"/>
     </row>
-    <row r="465" spans="1:25" ht="12.75">
+    <row r="465" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -13088,7 +13132,7 @@
       <c r="X465" s="1"/>
       <c r="Y465" s="1"/>
     </row>
-    <row r="466" spans="1:25" ht="12.75">
+    <row r="466" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -13115,7 +13159,7 @@
       <c r="X466" s="1"/>
       <c r="Y466" s="1"/>
     </row>
-    <row r="467" spans="1:25" ht="12.75">
+    <row r="467" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -13142,7 +13186,7 @@
       <c r="X467" s="1"/>
       <c r="Y467" s="1"/>
     </row>
-    <row r="468" spans="1:25" ht="12.75">
+    <row r="468" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -13169,7 +13213,7 @@
       <c r="X468" s="1"/>
       <c r="Y468" s="1"/>
     </row>
-    <row r="469" spans="1:25" ht="12.75">
+    <row r="469" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -13196,7 +13240,7 @@
       <c r="X469" s="1"/>
       <c r="Y469" s="1"/>
     </row>
-    <row r="470" spans="1:25" ht="12.75">
+    <row r="470" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -13223,7 +13267,7 @@
       <c r="X470" s="1"/>
       <c r="Y470" s="1"/>
     </row>
-    <row r="471" spans="1:25" ht="12.75">
+    <row r="471" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -13250,7 +13294,7 @@
       <c r="X471" s="1"/>
       <c r="Y471" s="1"/>
     </row>
-    <row r="472" spans="1:25" ht="12.75">
+    <row r="472" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -13277,7 +13321,7 @@
       <c r="X472" s="1"/>
       <c r="Y472" s="1"/>
     </row>
-    <row r="473" spans="1:25" ht="12.75">
+    <row r="473" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -13304,7 +13348,7 @@
       <c r="X473" s="1"/>
       <c r="Y473" s="1"/>
     </row>
-    <row r="474" spans="1:25" ht="12.75">
+    <row r="474" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -13331,7 +13375,7 @@
       <c r="X474" s="1"/>
       <c r="Y474" s="1"/>
     </row>
-    <row r="475" spans="1:25" ht="12.75">
+    <row r="475" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -13358,7 +13402,7 @@
       <c r="X475" s="1"/>
       <c r="Y475" s="1"/>
     </row>
-    <row r="476" spans="1:25" ht="12.75">
+    <row r="476" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -13385,7 +13429,7 @@
       <c r="X476" s="1"/>
       <c r="Y476" s="1"/>
     </row>
-    <row r="477" spans="1:25" ht="12.75">
+    <row r="477" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -13412,7 +13456,7 @@
       <c r="X477" s="1"/>
       <c r="Y477" s="1"/>
     </row>
-    <row r="478" spans="1:25" ht="12.75">
+    <row r="478" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -13439,7 +13483,7 @@
       <c r="X478" s="1"/>
       <c r="Y478" s="1"/>
     </row>
-    <row r="479" spans="1:25" ht="12.75">
+    <row r="479" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -13466,7 +13510,7 @@
       <c r="X479" s="1"/>
       <c r="Y479" s="1"/>
     </row>
-    <row r="480" spans="1:25" ht="12.75">
+    <row r="480" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -13493,7 +13537,7 @@
       <c r="X480" s="1"/>
       <c r="Y480" s="1"/>
     </row>
-    <row r="481" spans="1:25" ht="12.75">
+    <row r="481" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -13520,7 +13564,7 @@
       <c r="X481" s="1"/>
       <c r="Y481" s="1"/>
     </row>
-    <row r="482" spans="1:25" ht="12.75">
+    <row r="482" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -13547,7 +13591,7 @@
       <c r="X482" s="1"/>
       <c r="Y482" s="1"/>
     </row>
-    <row r="483" spans="1:25" ht="12.75">
+    <row r="483" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -13574,7 +13618,7 @@
       <c r="X483" s="1"/>
       <c r="Y483" s="1"/>
     </row>
-    <row r="484" spans="1:25" ht="12.75">
+    <row r="484" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -13601,7 +13645,7 @@
       <c r="X484" s="1"/>
       <c r="Y484" s="1"/>
     </row>
-    <row r="485" spans="1:25" ht="12.75">
+    <row r="485" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -13628,7 +13672,7 @@
       <c r="X485" s="1"/>
       <c r="Y485" s="1"/>
     </row>
-    <row r="486" spans="1:25" ht="12.75">
+    <row r="486" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -13655,7 +13699,7 @@
       <c r="X486" s="1"/>
       <c r="Y486" s="1"/>
     </row>
-    <row r="487" spans="1:25" ht="12.75">
+    <row r="487" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -13682,7 +13726,7 @@
       <c r="X487" s="1"/>
       <c r="Y487" s="1"/>
     </row>
-    <row r="488" spans="1:25" ht="12.75">
+    <row r="488" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -13709,7 +13753,7 @@
       <c r="X488" s="1"/>
       <c r="Y488" s="1"/>
     </row>
-    <row r="489" spans="1:25" ht="12.75">
+    <row r="489" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -13736,7 +13780,7 @@
       <c r="X489" s="1"/>
       <c r="Y489" s="1"/>
     </row>
-    <row r="490" spans="1:25" ht="12.75">
+    <row r="490" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -13763,7 +13807,7 @@
       <c r="X490" s="1"/>
       <c r="Y490" s="1"/>
     </row>
-    <row r="491" spans="1:25" ht="12.75">
+    <row r="491" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -13790,7 +13834,7 @@
       <c r="X491" s="1"/>
       <c r="Y491" s="1"/>
     </row>
-    <row r="492" spans="1:25" ht="12.75">
+    <row r="492" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -13817,7 +13861,7 @@
       <c r="X492" s="1"/>
       <c r="Y492" s="1"/>
     </row>
-    <row r="493" spans="1:25" ht="12.75">
+    <row r="493" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -13844,7 +13888,7 @@
       <c r="X493" s="1"/>
       <c r="Y493" s="1"/>
     </row>
-    <row r="494" spans="1:25" ht="12.75">
+    <row r="494" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -13871,7 +13915,7 @@
       <c r="X494" s="1"/>
       <c r="Y494" s="1"/>
     </row>
-    <row r="495" spans="1:25" ht="12.75">
+    <row r="495" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -13898,7 +13942,7 @@
       <c r="X495" s="1"/>
       <c r="Y495" s="1"/>
     </row>
-    <row r="496" spans="1:25" ht="12.75">
+    <row r="496" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -13925,7 +13969,7 @@
       <c r="X496" s="1"/>
       <c r="Y496" s="1"/>
     </row>
-    <row r="497" spans="1:25" ht="12.75">
+    <row r="497" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -13952,7 +13996,7 @@
       <c r="X497" s="1"/>
       <c r="Y497" s="1"/>
     </row>
-    <row r="498" spans="1:25" ht="12.75">
+    <row r="498" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -13979,7 +14023,7 @@
       <c r="X498" s="1"/>
       <c r="Y498" s="1"/>
     </row>
-    <row r="499" spans="1:25" ht="12.75">
+    <row r="499" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -14006,7 +14050,7 @@
       <c r="X499" s="1"/>
       <c r="Y499" s="1"/>
     </row>
-    <row r="500" spans="1:25" ht="12.75">
+    <row r="500" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -14033,7 +14077,7 @@
       <c r="X500" s="1"/>
       <c r="Y500" s="1"/>
     </row>
-    <row r="501" spans="1:25" ht="12.75">
+    <row r="501" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -14060,7 +14104,7 @@
       <c r="X501" s="1"/>
       <c r="Y501" s="1"/>
     </row>
-    <row r="502" spans="1:25" ht="12.75">
+    <row r="502" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -14087,7 +14131,7 @@
       <c r="X502" s="1"/>
       <c r="Y502" s="1"/>
     </row>
-    <row r="503" spans="1:25" ht="12.75">
+    <row r="503" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -14114,7 +14158,7 @@
       <c r="X503" s="1"/>
       <c r="Y503" s="1"/>
     </row>
-    <row r="504" spans="1:25" ht="12.75">
+    <row r="504" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -14141,7 +14185,7 @@
       <c r="X504" s="1"/>
       <c r="Y504" s="1"/>
     </row>
-    <row r="505" spans="1:25" ht="12.75">
+    <row r="505" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -14168,7 +14212,7 @@
       <c r="X505" s="1"/>
       <c r="Y505" s="1"/>
     </row>
-    <row r="506" spans="1:25" ht="12.75">
+    <row r="506" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -14195,7 +14239,7 @@
       <c r="X506" s="1"/>
       <c r="Y506" s="1"/>
     </row>
-    <row r="507" spans="1:25" ht="12.75">
+    <row r="507" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -14222,7 +14266,7 @@
       <c r="X507" s="1"/>
       <c r="Y507" s="1"/>
     </row>
-    <row r="508" spans="1:25" ht="12.75">
+    <row r="508" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -14249,7 +14293,7 @@
       <c r="X508" s="1"/>
       <c r="Y508" s="1"/>
     </row>
-    <row r="509" spans="1:25" ht="12.75">
+    <row r="509" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -14276,7 +14320,7 @@
       <c r="X509" s="1"/>
       <c r="Y509" s="1"/>
     </row>
-    <row r="510" spans="1:25" ht="12.75">
+    <row r="510" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -14303,7 +14347,7 @@
       <c r="X510" s="1"/>
       <c r="Y510" s="1"/>
     </row>
-    <row r="511" spans="1:25" ht="12.75">
+    <row r="511" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -14330,7 +14374,7 @@
       <c r="X511" s="1"/>
       <c r="Y511" s="1"/>
     </row>
-    <row r="512" spans="1:25" ht="12.75">
+    <row r="512" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -14357,7 +14401,7 @@
       <c r="X512" s="1"/>
       <c r="Y512" s="1"/>
     </row>
-    <row r="513" spans="1:25" ht="12.75">
+    <row r="513" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -14384,7 +14428,7 @@
       <c r="X513" s="1"/>
       <c r="Y513" s="1"/>
     </row>
-    <row r="514" spans="1:25" ht="12.75">
+    <row r="514" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -14411,7 +14455,7 @@
       <c r="X514" s="1"/>
       <c r="Y514" s="1"/>
     </row>
-    <row r="515" spans="1:25" ht="12.75">
+    <row r="515" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -14438,7 +14482,7 @@
       <c r="X515" s="1"/>
       <c r="Y515" s="1"/>
     </row>
-    <row r="516" spans="1:25" ht="12.75">
+    <row r="516" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -14465,7 +14509,7 @@
       <c r="X516" s="1"/>
       <c r="Y516" s="1"/>
     </row>
-    <row r="517" spans="1:25" ht="12.75">
+    <row r="517" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -14492,7 +14536,7 @@
       <c r="X517" s="1"/>
       <c r="Y517" s="1"/>
     </row>
-    <row r="518" spans="1:25" ht="12.75">
+    <row r="518" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -14519,7 +14563,7 @@
       <c r="X518" s="1"/>
       <c r="Y518" s="1"/>
     </row>
-    <row r="519" spans="1:25" ht="12.75">
+    <row r="519" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -14546,7 +14590,7 @@
       <c r="X519" s="1"/>
       <c r="Y519" s="1"/>
     </row>
-    <row r="520" spans="1:25" ht="12.75">
+    <row r="520" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -14573,7 +14617,7 @@
       <c r="X520" s="1"/>
       <c r="Y520" s="1"/>
     </row>
-    <row r="521" spans="1:25" ht="12.75">
+    <row r="521" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -14600,7 +14644,7 @@
       <c r="X521" s="1"/>
       <c r="Y521" s="1"/>
     </row>
-    <row r="522" spans="1:25" ht="12.75">
+    <row r="522" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -14627,7 +14671,7 @@
       <c r="X522" s="1"/>
       <c r="Y522" s="1"/>
     </row>
-    <row r="523" spans="1:25" ht="12.75">
+    <row r="523" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -14654,7 +14698,7 @@
       <c r="X523" s="1"/>
       <c r="Y523" s="1"/>
     </row>
-    <row r="524" spans="1:25" ht="12.75">
+    <row r="524" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -14681,7 +14725,7 @@
       <c r="X524" s="1"/>
       <c r="Y524" s="1"/>
     </row>
-    <row r="525" spans="1:25" ht="12.75">
+    <row r="525" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -14708,7 +14752,7 @@
       <c r="X525" s="1"/>
       <c r="Y525" s="1"/>
     </row>
-    <row r="526" spans="1:25" ht="12.75">
+    <row r="526" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -14735,7 +14779,7 @@
       <c r="X526" s="1"/>
       <c r="Y526" s="1"/>
     </row>
-    <row r="527" spans="1:25" ht="12.75">
+    <row r="527" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -14762,7 +14806,7 @@
       <c r="X527" s="1"/>
       <c r="Y527" s="1"/>
     </row>
-    <row r="528" spans="1:25" ht="12.75">
+    <row r="528" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -14789,7 +14833,7 @@
       <c r="X528" s="1"/>
       <c r="Y528" s="1"/>
     </row>
-    <row r="529" spans="1:25" ht="12.75">
+    <row r="529" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -14816,7 +14860,7 @@
       <c r="X529" s="1"/>
       <c r="Y529" s="1"/>
     </row>
-    <row r="530" spans="1:25" ht="12.75">
+    <row r="530" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -14843,7 +14887,7 @@
       <c r="X530" s="1"/>
       <c r="Y530" s="1"/>
     </row>
-    <row r="531" spans="1:25" ht="12.75">
+    <row r="531" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -14870,7 +14914,7 @@
       <c r="X531" s="1"/>
       <c r="Y531" s="1"/>
     </row>
-    <row r="532" spans="1:25" ht="12.75">
+    <row r="532" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -14897,7 +14941,7 @@
       <c r="X532" s="1"/>
       <c r="Y532" s="1"/>
     </row>
-    <row r="533" spans="1:25" ht="12.75">
+    <row r="533" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -14924,7 +14968,7 @@
       <c r="X533" s="1"/>
       <c r="Y533" s="1"/>
     </row>
-    <row r="534" spans="1:25" ht="12.75">
+    <row r="534" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -14951,7 +14995,7 @@
       <c r="X534" s="1"/>
       <c r="Y534" s="1"/>
     </row>
-    <row r="535" spans="1:25" ht="12.75">
+    <row r="535" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -14978,7 +15022,7 @@
       <c r="X535" s="1"/>
       <c r="Y535" s="1"/>
     </row>
-    <row r="536" spans="1:25" ht="12.75">
+    <row r="536" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -15005,7 +15049,7 @@
       <c r="X536" s="1"/>
       <c r="Y536" s="1"/>
     </row>
-    <row r="537" spans="1:25" ht="12.75">
+    <row r="537" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -15032,7 +15076,7 @@
       <c r="X537" s="1"/>
       <c r="Y537" s="1"/>
     </row>
-    <row r="538" spans="1:25" ht="12.75">
+    <row r="538" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -15059,7 +15103,7 @@
       <c r="X538" s="1"/>
       <c r="Y538" s="1"/>
     </row>
-    <row r="539" spans="1:25" ht="12.75">
+    <row r="539" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -15086,7 +15130,7 @@
       <c r="X539" s="1"/>
       <c r="Y539" s="1"/>
     </row>
-    <row r="540" spans="1:25" ht="12.75">
+    <row r="540" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -15113,7 +15157,7 @@
       <c r="X540" s="1"/>
       <c r="Y540" s="1"/>
     </row>
-    <row r="541" spans="1:25" ht="12.75">
+    <row r="541" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -15140,7 +15184,7 @@
       <c r="X541" s="1"/>
       <c r="Y541" s="1"/>
     </row>
-    <row r="542" spans="1:25" ht="12.75">
+    <row r="542" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -15167,7 +15211,7 @@
       <c r="X542" s="1"/>
       <c r="Y542" s="1"/>
     </row>
-    <row r="543" spans="1:25" ht="12.75">
+    <row r="543" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -15194,7 +15238,7 @@
       <c r="X543" s="1"/>
       <c r="Y543" s="1"/>
     </row>
-    <row r="544" spans="1:25" ht="12.75">
+    <row r="544" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -15221,7 +15265,7 @@
       <c r="X544" s="1"/>
       <c r="Y544" s="1"/>
     </row>
-    <row r="545" spans="1:25" ht="12.75">
+    <row r="545" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -15248,7 +15292,7 @@
       <c r="X545" s="1"/>
       <c r="Y545" s="1"/>
     </row>
-    <row r="546" spans="1:25" ht="12.75">
+    <row r="546" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -15275,7 +15319,7 @@
       <c r="X546" s="1"/>
       <c r="Y546" s="1"/>
     </row>
-    <row r="547" spans="1:25" ht="12.75">
+    <row r="547" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -15302,7 +15346,7 @@
       <c r="X547" s="1"/>
       <c r="Y547" s="1"/>
     </row>
-    <row r="548" spans="1:25" ht="12.75">
+    <row r="548" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -15329,7 +15373,7 @@
       <c r="X548" s="1"/>
       <c r="Y548" s="1"/>
     </row>
-    <row r="549" spans="1:25" ht="12.75">
+    <row r="549" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -15356,7 +15400,7 @@
       <c r="X549" s="1"/>
       <c r="Y549" s="1"/>
     </row>
-    <row r="550" spans="1:25" ht="12.75">
+    <row r="550" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -15383,7 +15427,7 @@
       <c r="X550" s="1"/>
       <c r="Y550" s="1"/>
     </row>
-    <row r="551" spans="1:25" ht="12.75">
+    <row r="551" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -15410,7 +15454,7 @@
       <c r="X551" s="1"/>
       <c r="Y551" s="1"/>
     </row>
-    <row r="552" spans="1:25" ht="12.75">
+    <row r="552" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -15437,7 +15481,7 @@
       <c r="X552" s="1"/>
       <c r="Y552" s="1"/>
     </row>
-    <row r="553" spans="1:25" ht="12.75">
+    <row r="553" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -15464,7 +15508,7 @@
       <c r="X553" s="1"/>
       <c r="Y553" s="1"/>
     </row>
-    <row r="554" spans="1:25" ht="12.75">
+    <row r="554" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -15491,7 +15535,7 @@
       <c r="X554" s="1"/>
       <c r="Y554" s="1"/>
     </row>
-    <row r="555" spans="1:25" ht="12.75">
+    <row r="555" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -15518,7 +15562,7 @@
       <c r="X555" s="1"/>
       <c r="Y555" s="1"/>
     </row>
-    <row r="556" spans="1:25" ht="12.75">
+    <row r="556" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -15545,7 +15589,7 @@
       <c r="X556" s="1"/>
       <c r="Y556" s="1"/>
     </row>
-    <row r="557" spans="1:25" ht="12.75">
+    <row r="557" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -15572,7 +15616,7 @@
       <c r="X557" s="1"/>
       <c r="Y557" s="1"/>
     </row>
-    <row r="558" spans="1:25" ht="12.75">
+    <row r="558" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -15599,7 +15643,7 @@
       <c r="X558" s="1"/>
       <c r="Y558" s="1"/>
     </row>
-    <row r="559" spans="1:25" ht="12.75">
+    <row r="559" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -15626,7 +15670,7 @@
       <c r="X559" s="1"/>
       <c r="Y559" s="1"/>
     </row>
-    <row r="560" spans="1:25" ht="12.75">
+    <row r="560" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -15653,7 +15697,7 @@
       <c r="X560" s="1"/>
       <c r="Y560" s="1"/>
     </row>
-    <row r="561" spans="1:25" ht="12.75">
+    <row r="561" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -15680,7 +15724,7 @@
       <c r="X561" s="1"/>
       <c r="Y561" s="1"/>
     </row>
-    <row r="562" spans="1:25" ht="12.75">
+    <row r="562" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -15707,7 +15751,7 @@
       <c r="X562" s="1"/>
       <c r="Y562" s="1"/>
     </row>
-    <row r="563" spans="1:25" ht="12.75">
+    <row r="563" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -15734,7 +15778,7 @@
       <c r="X563" s="1"/>
       <c r="Y563" s="1"/>
     </row>
-    <row r="564" spans="1:25" ht="12.75">
+    <row r="564" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -15761,7 +15805,7 @@
       <c r="X564" s="1"/>
       <c r="Y564" s="1"/>
     </row>
-    <row r="565" spans="1:25" ht="12.75">
+    <row r="565" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -15788,7 +15832,7 @@
       <c r="X565" s="1"/>
       <c r="Y565" s="1"/>
     </row>
-    <row r="566" spans="1:25" ht="12.75">
+    <row r="566" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -15815,7 +15859,7 @@
       <c r="X566" s="1"/>
       <c r="Y566" s="1"/>
     </row>
-    <row r="567" spans="1:25" ht="12.75">
+    <row r="567" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -15842,7 +15886,7 @@
       <c r="X567" s="1"/>
       <c r="Y567" s="1"/>
     </row>
-    <row r="568" spans="1:25" ht="12.75">
+    <row r="568" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -15869,7 +15913,7 @@
       <c r="X568" s="1"/>
       <c r="Y568" s="1"/>
     </row>
-    <row r="569" spans="1:25" ht="12.75">
+    <row r="569" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -15896,7 +15940,7 @@
       <c r="X569" s="1"/>
       <c r="Y569" s="1"/>
     </row>
-    <row r="570" spans="1:25" ht="12.75">
+    <row r="570" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -15923,7 +15967,7 @@
       <c r="X570" s="1"/>
       <c r="Y570" s="1"/>
     </row>
-    <row r="571" spans="1:25" ht="12.75">
+    <row r="571" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -15950,7 +15994,7 @@
       <c r="X571" s="1"/>
       <c r="Y571" s="1"/>
     </row>
-    <row r="572" spans="1:25" ht="12.75">
+    <row r="572" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -15977,7 +16021,7 @@
       <c r="X572" s="1"/>
       <c r="Y572" s="1"/>
     </row>
-    <row r="573" spans="1:25" ht="12.75">
+    <row r="573" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -16004,7 +16048,7 @@
       <c r="X573" s="1"/>
       <c r="Y573" s="1"/>
     </row>
-    <row r="574" spans="1:25" ht="12.75">
+    <row r="574" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -16031,7 +16075,7 @@
       <c r="X574" s="1"/>
       <c r="Y574" s="1"/>
     </row>
-    <row r="575" spans="1:25" ht="12.75">
+    <row r="575" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -16058,7 +16102,7 @@
       <c r="X575" s="1"/>
       <c r="Y575" s="1"/>
     </row>
-    <row r="576" spans="1:25" ht="12.75">
+    <row r="576" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -16085,7 +16129,7 @@
       <c r="X576" s="1"/>
       <c r="Y576" s="1"/>
     </row>
-    <row r="577" spans="1:25" ht="12.75">
+    <row r="577" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -16112,7 +16156,7 @@
       <c r="X577" s="1"/>
       <c r="Y577" s="1"/>
     </row>
-    <row r="578" spans="1:25" ht="12.75">
+    <row r="578" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -16139,7 +16183,7 @@
       <c r="X578" s="1"/>
       <c r="Y578" s="1"/>
     </row>
-    <row r="579" spans="1:25" ht="12.75">
+    <row r="579" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -16166,7 +16210,7 @@
       <c r="X579" s="1"/>
       <c r="Y579" s="1"/>
     </row>
-    <row r="580" spans="1:25" ht="12.75">
+    <row r="580" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -16193,7 +16237,7 @@
       <c r="X580" s="1"/>
       <c r="Y580" s="1"/>
     </row>
-    <row r="581" spans="1:25" ht="12.75">
+    <row r="581" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -16220,7 +16264,7 @@
       <c r="X581" s="1"/>
       <c r="Y581" s="1"/>
     </row>
-    <row r="582" spans="1:25" ht="12.75">
+    <row r="582" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -16247,7 +16291,7 @@
       <c r="X582" s="1"/>
       <c r="Y582" s="1"/>
     </row>
-    <row r="583" spans="1:25" ht="12.75">
+    <row r="583" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -16274,7 +16318,7 @@
       <c r="X583" s="1"/>
       <c r="Y583" s="1"/>
     </row>
-    <row r="584" spans="1:25" ht="12.75">
+    <row r="584" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -16301,7 +16345,7 @@
       <c r="X584" s="1"/>
       <c r="Y584" s="1"/>
     </row>
-    <row r="585" spans="1:25" ht="12.75">
+    <row r="585" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -16328,7 +16372,7 @@
       <c r="X585" s="1"/>
       <c r="Y585" s="1"/>
     </row>
-    <row r="586" spans="1:25" ht="12.75">
+    <row r="586" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -16355,7 +16399,7 @@
       <c r="X586" s="1"/>
       <c r="Y586" s="1"/>
     </row>
-    <row r="587" spans="1:25" ht="12.75">
+    <row r="587" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -16382,7 +16426,7 @@
       <c r="X587" s="1"/>
       <c r="Y587" s="1"/>
     </row>
-    <row r="588" spans="1:25" ht="12.75">
+    <row r="588" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -16409,7 +16453,7 @@
       <c r="X588" s="1"/>
       <c r="Y588" s="1"/>
     </row>
-    <row r="589" spans="1:25" ht="12.75">
+    <row r="589" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -16436,7 +16480,7 @@
       <c r="X589" s="1"/>
       <c r="Y589" s="1"/>
     </row>
-    <row r="590" spans="1:25" ht="12.75">
+    <row r="590" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -16463,7 +16507,7 @@
       <c r="X590" s="1"/>
       <c r="Y590" s="1"/>
     </row>
-    <row r="591" spans="1:25" ht="12.75">
+    <row r="591" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -16490,7 +16534,7 @@
       <c r="X591" s="1"/>
       <c r="Y591" s="1"/>
     </row>
-    <row r="592" spans="1:25" ht="12.75">
+    <row r="592" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -16517,7 +16561,7 @@
       <c r="X592" s="1"/>
       <c r="Y592" s="1"/>
     </row>
-    <row r="593" spans="1:25" ht="12.75">
+    <row r="593" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -16544,7 +16588,7 @@
       <c r="X593" s="1"/>
       <c r="Y593" s="1"/>
     </row>
-    <row r="594" spans="1:25" ht="12.75">
+    <row r="594" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -16571,7 +16615,7 @@
       <c r="X594" s="1"/>
       <c r="Y594" s="1"/>
     </row>
-    <row r="595" spans="1:25" ht="12.75">
+    <row r="595" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -16598,7 +16642,7 @@
       <c r="X595" s="1"/>
       <c r="Y595" s="1"/>
     </row>
-    <row r="596" spans="1:25" ht="12.75">
+    <row r="596" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -16625,7 +16669,7 @@
       <c r="X596" s="1"/>
       <c r="Y596" s="1"/>
     </row>
-    <row r="597" spans="1:25" ht="12.75">
+    <row r="597" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -16652,7 +16696,7 @@
       <c r="X597" s="1"/>
       <c r="Y597" s="1"/>
     </row>
-    <row r="598" spans="1:25" ht="12.75">
+    <row r="598" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -16679,7 +16723,7 @@
       <c r="X598" s="1"/>
       <c r="Y598" s="1"/>
     </row>
-    <row r="599" spans="1:25" ht="12.75">
+    <row r="599" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -16706,7 +16750,7 @@
       <c r="X599" s="1"/>
       <c r="Y599" s="1"/>
     </row>
-    <row r="600" spans="1:25" ht="12.75">
+    <row r="600" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -16733,7 +16777,7 @@
       <c r="X600" s="1"/>
       <c r="Y600" s="1"/>
     </row>
-    <row r="601" spans="1:25" ht="12.75">
+    <row r="601" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -16760,7 +16804,7 @@
       <c r="X601" s="1"/>
       <c r="Y601" s="1"/>
     </row>
-    <row r="602" spans="1:25" ht="12.75">
+    <row r="602" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -16787,7 +16831,7 @@
       <c r="X602" s="1"/>
       <c r="Y602" s="1"/>
     </row>
-    <row r="603" spans="1:25" ht="12.75">
+    <row r="603" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -16814,7 +16858,7 @@
       <c r="X603" s="1"/>
       <c r="Y603" s="1"/>
     </row>
-    <row r="604" spans="1:25" ht="12.75">
+    <row r="604" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -16841,7 +16885,7 @@
       <c r="X604" s="1"/>
       <c r="Y604" s="1"/>
     </row>
-    <row r="605" spans="1:25" ht="12.75">
+    <row r="605" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -16868,7 +16912,7 @@
       <c r="X605" s="1"/>
       <c r="Y605" s="1"/>
     </row>
-    <row r="606" spans="1:25" ht="12.75">
+    <row r="606" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -16895,7 +16939,7 @@
       <c r="X606" s="1"/>
       <c r="Y606" s="1"/>
     </row>
-    <row r="607" spans="1:25" ht="12.75">
+    <row r="607" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -16922,7 +16966,7 @@
       <c r="X607" s="1"/>
       <c r="Y607" s="1"/>
     </row>
-    <row r="608" spans="1:25" ht="12.75">
+    <row r="608" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -16949,7 +16993,7 @@
       <c r="X608" s="1"/>
       <c r="Y608" s="1"/>
     </row>
-    <row r="609" spans="1:25" ht="12.75">
+    <row r="609" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -16976,7 +17020,7 @@
       <c r="X609" s="1"/>
       <c r="Y609" s="1"/>
     </row>
-    <row r="610" spans="1:25" ht="12.75">
+    <row r="610" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -17003,7 +17047,7 @@
       <c r="X610" s="1"/>
       <c r="Y610" s="1"/>
     </row>
-    <row r="611" spans="1:25" ht="12.75">
+    <row r="611" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -17030,7 +17074,7 @@
       <c r="X611" s="1"/>
       <c r="Y611" s="1"/>
     </row>
-    <row r="612" spans="1:25" ht="12.75">
+    <row r="612" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -17057,7 +17101,7 @@
       <c r="X612" s="1"/>
       <c r="Y612" s="1"/>
     </row>
-    <row r="613" spans="1:25" ht="12.75">
+    <row r="613" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -17084,7 +17128,7 @@
       <c r="X613" s="1"/>
       <c r="Y613" s="1"/>
     </row>
-    <row r="614" spans="1:25" ht="12.75">
+    <row r="614" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -17111,7 +17155,7 @@
       <c r="X614" s="1"/>
       <c r="Y614" s="1"/>
     </row>
-    <row r="615" spans="1:25" ht="12.75">
+    <row r="615" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -17138,7 +17182,7 @@
       <c r="X615" s="1"/>
       <c r="Y615" s="1"/>
     </row>
-    <row r="616" spans="1:25" ht="12.75">
+    <row r="616" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -17165,7 +17209,7 @@
       <c r="X616" s="1"/>
       <c r="Y616" s="1"/>
     </row>
-    <row r="617" spans="1:25" ht="12.75">
+    <row r="617" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -17192,7 +17236,7 @@
       <c r="X617" s="1"/>
       <c r="Y617" s="1"/>
     </row>
-    <row r="618" spans="1:25" ht="12.75">
+    <row r="618" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -17219,7 +17263,7 @@
       <c r="X618" s="1"/>
       <c r="Y618" s="1"/>
     </row>
-    <row r="619" spans="1:25" ht="12.75">
+    <row r="619" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -17246,7 +17290,7 @@
       <c r="X619" s="1"/>
       <c r="Y619" s="1"/>
     </row>
-    <row r="620" spans="1:25" ht="12.75">
+    <row r="620" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -17273,7 +17317,7 @@
       <c r="X620" s="1"/>
       <c r="Y620" s="1"/>
     </row>
-    <row r="621" spans="1:25" ht="12.75">
+    <row r="621" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -17300,7 +17344,7 @@
       <c r="X621" s="1"/>
       <c r="Y621" s="1"/>
     </row>
-    <row r="622" spans="1:25" ht="12.75">
+    <row r="622" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -17327,7 +17371,7 @@
       <c r="X622" s="1"/>
       <c r="Y622" s="1"/>
     </row>
-    <row r="623" spans="1:25" ht="12.75">
+    <row r="623" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -17354,7 +17398,7 @@
       <c r="X623" s="1"/>
       <c r="Y623" s="1"/>
     </row>
-    <row r="624" spans="1:25" ht="12.75">
+    <row r="624" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -17381,7 +17425,7 @@
       <c r="X624" s="1"/>
       <c r="Y624" s="1"/>
     </row>
-    <row r="625" spans="1:25" ht="12.75">
+    <row r="625" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -17408,7 +17452,7 @@
       <c r="X625" s="1"/>
       <c r="Y625" s="1"/>
     </row>
-    <row r="626" spans="1:25" ht="12.75">
+    <row r="626" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -17435,7 +17479,7 @@
       <c r="X626" s="1"/>
       <c r="Y626" s="1"/>
     </row>
-    <row r="627" spans="1:25" ht="12.75">
+    <row r="627" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -17462,7 +17506,7 @@
       <c r="X627" s="1"/>
       <c r="Y627" s="1"/>
     </row>
-    <row r="628" spans="1:25" ht="12.75">
+    <row r="628" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -17489,7 +17533,7 @@
       <c r="X628" s="1"/>
       <c r="Y628" s="1"/>
     </row>
-    <row r="629" spans="1:25" ht="12.75">
+    <row r="629" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -17516,7 +17560,7 @@
       <c r="X629" s="1"/>
       <c r="Y629" s="1"/>
     </row>
-    <row r="630" spans="1:25" ht="12.75">
+    <row r="630" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -17543,7 +17587,7 @@
       <c r="X630" s="1"/>
       <c r="Y630" s="1"/>
     </row>
-    <row r="631" spans="1:25" ht="12.75">
+    <row r="631" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -17570,7 +17614,7 @@
       <c r="X631" s="1"/>
       <c r="Y631" s="1"/>
     </row>
-    <row r="632" spans="1:25" ht="12.75">
+    <row r="632" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -17597,7 +17641,7 @@
       <c r="X632" s="1"/>
       <c r="Y632" s="1"/>
     </row>
-    <row r="633" spans="1:25" ht="12.75">
+    <row r="633" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -17624,7 +17668,7 @@
       <c r="X633" s="1"/>
       <c r="Y633" s="1"/>
     </row>
-    <row r="634" spans="1:25" ht="12.75">
+    <row r="634" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -17651,7 +17695,7 @@
       <c r="X634" s="1"/>
       <c r="Y634" s="1"/>
     </row>
-    <row r="635" spans="1:25" ht="12.75">
+    <row r="635" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -17678,7 +17722,7 @@
       <c r="X635" s="1"/>
       <c r="Y635" s="1"/>
     </row>
-    <row r="636" spans="1:25" ht="12.75">
+    <row r="636" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -17705,7 +17749,7 @@
       <c r="X636" s="1"/>
       <c r="Y636" s="1"/>
     </row>
-    <row r="637" spans="1:25" ht="12.75">
+    <row r="637" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -17732,7 +17776,7 @@
       <c r="X637" s="1"/>
       <c r="Y637" s="1"/>
     </row>
-    <row r="638" spans="1:25" ht="12.75">
+    <row r="638" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -17759,7 +17803,7 @@
       <c r="X638" s="1"/>
       <c r="Y638" s="1"/>
     </row>
-    <row r="639" spans="1:25" ht="12.75">
+    <row r="639" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -17786,7 +17830,7 @@
       <c r="X639" s="1"/>
       <c r="Y639" s="1"/>
     </row>
-    <row r="640" spans="1:25" ht="12.75">
+    <row r="640" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -17813,7 +17857,7 @@
       <c r="X640" s="1"/>
       <c r="Y640" s="1"/>
     </row>
-    <row r="641" spans="1:25" ht="12.75">
+    <row r="641" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -17840,7 +17884,7 @@
       <c r="X641" s="1"/>
       <c r="Y641" s="1"/>
     </row>
-    <row r="642" spans="1:25" ht="12.75">
+    <row r="642" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -17867,7 +17911,7 @@
       <c r="X642" s="1"/>
       <c r="Y642" s="1"/>
     </row>
-    <row r="643" spans="1:25" ht="12.75">
+    <row r="643" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -17894,7 +17938,7 @@
       <c r="X643" s="1"/>
       <c r="Y643" s="1"/>
     </row>
-    <row r="644" spans="1:25" ht="12.75">
+    <row r="644" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -17921,7 +17965,7 @@
       <c r="X644" s="1"/>
       <c r="Y644" s="1"/>
     </row>
-    <row r="645" spans="1:25" ht="12.75">
+    <row r="645" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -17948,7 +17992,7 @@
       <c r="X645" s="1"/>
       <c r="Y645" s="1"/>
     </row>
-    <row r="646" spans="1:25" ht="12.75">
+    <row r="646" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -17975,7 +18019,7 @@
       <c r="X646" s="1"/>
       <c r="Y646" s="1"/>
     </row>
-    <row r="647" spans="1:25" ht="12.75">
+    <row r="647" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -18002,7 +18046,7 @@
       <c r="X647" s="1"/>
       <c r="Y647" s="1"/>
     </row>
-    <row r="648" spans="1:25" ht="12.75">
+    <row r="648" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -18029,7 +18073,7 @@
       <c r="X648" s="1"/>
       <c r="Y648" s="1"/>
     </row>
-    <row r="649" spans="1:25" ht="12.75">
+    <row r="649" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -18056,7 +18100,7 @@
       <c r="X649" s="1"/>
       <c r="Y649" s="1"/>
     </row>
-    <row r="650" spans="1:25" ht="12.75">
+    <row r="650" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -18083,7 +18127,7 @@
       <c r="X650" s="1"/>
       <c r="Y650" s="1"/>
     </row>
-    <row r="651" spans="1:25" ht="12.75">
+    <row r="651" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -18110,7 +18154,7 @@
       <c r="X651" s="1"/>
       <c r="Y651" s="1"/>
     </row>
-    <row r="652" spans="1:25" ht="12.75">
+    <row r="652" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -18137,7 +18181,7 @@
       <c r="X652" s="1"/>
       <c r="Y652" s="1"/>
     </row>
-    <row r="653" spans="1:25" ht="12.75">
+    <row r="653" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -18164,7 +18208,7 @@
       <c r="X653" s="1"/>
       <c r="Y653" s="1"/>
     </row>
-    <row r="654" spans="1:25" ht="12.75">
+    <row r="654" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -18191,7 +18235,7 @@
       <c r="X654" s="1"/>
       <c r="Y654" s="1"/>
     </row>
-    <row r="655" spans="1:25" ht="12.75">
+    <row r="655" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -18218,7 +18262,7 @@
       <c r="X655" s="1"/>
       <c r="Y655" s="1"/>
     </row>
-    <row r="656" spans="1:25" ht="12.75">
+    <row r="656" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -18245,7 +18289,7 @@
       <c r="X656" s="1"/>
       <c r="Y656" s="1"/>
     </row>
-    <row r="657" spans="1:25" ht="12.75">
+    <row r="657" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -18272,7 +18316,7 @@
       <c r="X657" s="1"/>
       <c r="Y657" s="1"/>
     </row>
-    <row r="658" spans="1:25" ht="12.75">
+    <row r="658" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -18299,7 +18343,7 @@
       <c r="X658" s="1"/>
       <c r="Y658" s="1"/>
     </row>
-    <row r="659" spans="1:25" ht="12.75">
+    <row r="659" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -18326,7 +18370,7 @@
       <c r="X659" s="1"/>
       <c r="Y659" s="1"/>
     </row>
-    <row r="660" spans="1:25" ht="12.75">
+    <row r="660" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -18353,7 +18397,7 @@
       <c r="X660" s="1"/>
       <c r="Y660" s="1"/>
     </row>
-    <row r="661" spans="1:25" ht="12.75">
+    <row r="661" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -18380,7 +18424,7 @@
       <c r="X661" s="1"/>
       <c r="Y661" s="1"/>
     </row>
-    <row r="662" spans="1:25" ht="12.75">
+    <row r="662" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -18407,7 +18451,7 @@
       <c r="X662" s="1"/>
       <c r="Y662" s="1"/>
     </row>
-    <row r="663" spans="1:25" ht="12.75">
+    <row r="663" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -18434,7 +18478,7 @@
       <c r="X663" s="1"/>
       <c r="Y663" s="1"/>
     </row>
-    <row r="664" spans="1:25" ht="12.75">
+    <row r="664" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -18461,7 +18505,7 @@
       <c r="X664" s="1"/>
       <c r="Y664" s="1"/>
     </row>
-    <row r="665" spans="1:25" ht="12.75">
+    <row r="665" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -18488,7 +18532,7 @@
       <c r="X665" s="1"/>
       <c r="Y665" s="1"/>
     </row>
-    <row r="666" spans="1:25" ht="12.75">
+    <row r="666" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -18515,7 +18559,7 @@
       <c r="X666" s="1"/>
       <c r="Y666" s="1"/>
     </row>
-    <row r="667" spans="1:25" ht="12.75">
+    <row r="667" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -18542,7 +18586,7 @@
       <c r="X667" s="1"/>
       <c r="Y667" s="1"/>
     </row>
-    <row r="668" spans="1:25" ht="12.75">
+    <row r="668" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -18569,7 +18613,7 @@
       <c r="X668" s="1"/>
       <c r="Y668" s="1"/>
     </row>
-    <row r="669" spans="1:25" ht="12.75">
+    <row r="669" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -18596,7 +18640,7 @@
       <c r="X669" s="1"/>
       <c r="Y669" s="1"/>
     </row>
-    <row r="670" spans="1:25" ht="12.75">
+    <row r="670" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -18623,7 +18667,7 @@
       <c r="X670" s="1"/>
       <c r="Y670" s="1"/>
     </row>
-    <row r="671" spans="1:25" ht="12.75">
+    <row r="671" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -18650,7 +18694,7 @@
       <c r="X671" s="1"/>
       <c r="Y671" s="1"/>
     </row>
-    <row r="672" spans="1:25" ht="12.75">
+    <row r="672" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -18677,7 +18721,7 @@
       <c r="X672" s="1"/>
       <c r="Y672" s="1"/>
     </row>
-    <row r="673" spans="1:25" ht="12.75">
+    <row r="673" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -18704,7 +18748,7 @@
       <c r="X673" s="1"/>
       <c r="Y673" s="1"/>
     </row>
-    <row r="674" spans="1:25" ht="12.75">
+    <row r="674" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -18731,7 +18775,7 @@
       <c r="X674" s="1"/>
       <c r="Y674" s="1"/>
     </row>
-    <row r="675" spans="1:25" ht="12.75">
+    <row r="675" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -18758,7 +18802,7 @@
       <c r="X675" s="1"/>
       <c r="Y675" s="1"/>
     </row>
-    <row r="676" spans="1:25" ht="12.75">
+    <row r="676" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -18785,7 +18829,7 @@
       <c r="X676" s="1"/>
       <c r="Y676" s="1"/>
     </row>
-    <row r="677" spans="1:25" ht="12.75">
+    <row r="677" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -18812,7 +18856,7 @@
       <c r="X677" s="1"/>
       <c r="Y677" s="1"/>
     </row>
-    <row r="678" spans="1:25" ht="12.75">
+    <row r="678" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -18839,7 +18883,7 @@
       <c r="X678" s="1"/>
       <c r="Y678" s="1"/>
     </row>
-    <row r="679" spans="1:25" ht="12.75">
+    <row r="679" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -18866,7 +18910,7 @@
       <c r="X679" s="1"/>
       <c r="Y679" s="1"/>
     </row>
-    <row r="680" spans="1:25" ht="12.75">
+    <row r="680" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -18893,7 +18937,7 @@
       <c r="X680" s="1"/>
       <c r="Y680" s="1"/>
     </row>
-    <row r="681" spans="1:25" ht="12.75">
+    <row r="681" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -18920,7 +18964,7 @@
       <c r="X681" s="1"/>
       <c r="Y681" s="1"/>
     </row>
-    <row r="682" spans="1:25" ht="12.75">
+    <row r="682" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -18947,7 +18991,7 @@
       <c r="X682" s="1"/>
       <c r="Y682" s="1"/>
     </row>
-    <row r="683" spans="1:25" ht="12.75">
+    <row r="683" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -18974,7 +19018,7 @@
       <c r="X683" s="1"/>
       <c r="Y683" s="1"/>
     </row>
-    <row r="684" spans="1:25" ht="12.75">
+    <row r="684" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -19001,7 +19045,7 @@
       <c r="X684" s="1"/>
       <c r="Y684" s="1"/>
     </row>
-    <row r="685" spans="1:25" ht="12.75">
+    <row r="685" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -19028,7 +19072,7 @@
       <c r="X685" s="1"/>
       <c r="Y685" s="1"/>
     </row>
-    <row r="686" spans="1:25" ht="12.75">
+    <row r="686" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -19055,7 +19099,7 @@
       <c r="X686" s="1"/>
       <c r="Y686" s="1"/>
     </row>
-    <row r="687" spans="1:25" ht="12.75">
+    <row r="687" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -19082,7 +19126,7 @@
       <c r="X687" s="1"/>
       <c r="Y687" s="1"/>
     </row>
-    <row r="688" spans="1:25" ht="12.75">
+    <row r="688" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -19109,7 +19153,7 @@
       <c r="X688" s="1"/>
       <c r="Y688" s="1"/>
     </row>
-    <row r="689" spans="1:25" ht="12.75">
+    <row r="689" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -19136,7 +19180,7 @@
       <c r="X689" s="1"/>
       <c r="Y689" s="1"/>
     </row>
-    <row r="690" spans="1:25" ht="12.75">
+    <row r="690" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -19163,7 +19207,7 @@
       <c r="X690" s="1"/>
       <c r="Y690" s="1"/>
     </row>
-    <row r="691" spans="1:25" ht="12.75">
+    <row r="691" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -19190,7 +19234,7 @@
       <c r="X691" s="1"/>
       <c r="Y691" s="1"/>
     </row>
-    <row r="692" spans="1:25" ht="12.75">
+    <row r="692" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -19217,7 +19261,7 @@
       <c r="X692" s="1"/>
       <c r="Y692" s="1"/>
     </row>
-    <row r="693" spans="1:25" ht="12.75">
+    <row r="693" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -19244,7 +19288,7 @@
       <c r="X693" s="1"/>
       <c r="Y693" s="1"/>
     </row>
-    <row r="694" spans="1:25" ht="12.75">
+    <row r="694" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -19271,7 +19315,7 @@
       <c r="X694" s="1"/>
       <c r="Y694" s="1"/>
     </row>
-    <row r="695" spans="1:25" ht="12.75">
+    <row r="695" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -19298,7 +19342,7 @@
       <c r="X695" s="1"/>
       <c r="Y695" s="1"/>
     </row>
-    <row r="696" spans="1:25" ht="12.75">
+    <row r="696" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -19325,7 +19369,7 @@
       <c r="X696" s="1"/>
       <c r="Y696" s="1"/>
     </row>
-    <row r="697" spans="1:25" ht="12.75">
+    <row r="697" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -19352,7 +19396,7 @@
       <c r="X697" s="1"/>
       <c r="Y697" s="1"/>
     </row>
-    <row r="698" spans="1:25" ht="12.75">
+    <row r="698" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -19379,7 +19423,7 @@
       <c r="X698" s="1"/>
       <c r="Y698" s="1"/>
     </row>
-    <row r="699" spans="1:25" ht="12.75">
+    <row r="699" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -19406,7 +19450,7 @@
       <c r="X699" s="1"/>
       <c r="Y699" s="1"/>
     </row>
-    <row r="700" spans="1:25" ht="12.75">
+    <row r="700" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -19433,7 +19477,7 @@
       <c r="X700" s="1"/>
       <c r="Y700" s="1"/>
     </row>
-    <row r="701" spans="1:25" ht="12.75">
+    <row r="701" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -19460,7 +19504,7 @@
       <c r="X701" s="1"/>
       <c r="Y701" s="1"/>
     </row>
-    <row r="702" spans="1:25" ht="12.75">
+    <row r="702" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -19487,7 +19531,7 @@
       <c r="X702" s="1"/>
       <c r="Y702" s="1"/>
     </row>
-    <row r="703" spans="1:25" ht="12.75">
+    <row r="703" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -19514,7 +19558,7 @@
       <c r="X703" s="1"/>
       <c r="Y703" s="1"/>
     </row>
-    <row r="704" spans="1:25" ht="12.75">
+    <row r="704" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -19541,7 +19585,7 @@
       <c r="X704" s="1"/>
       <c r="Y704" s="1"/>
     </row>
-    <row r="705" spans="1:25" ht="12.75">
+    <row r="705" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -19568,7 +19612,7 @@
       <c r="X705" s="1"/>
       <c r="Y705" s="1"/>
     </row>
-    <row r="706" spans="1:25" ht="12.75">
+    <row r="706" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -19595,7 +19639,7 @@
       <c r="X706" s="1"/>
       <c r="Y706" s="1"/>
     </row>
-    <row r="707" spans="1:25" ht="12.75">
+    <row r="707" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -19622,7 +19666,7 @@
       <c r="X707" s="1"/>
       <c r="Y707" s="1"/>
     </row>
-    <row r="708" spans="1:25" ht="12.75">
+    <row r="708" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -19649,7 +19693,7 @@
       <c r="X708" s="1"/>
       <c r="Y708" s="1"/>
     </row>
-    <row r="709" spans="1:25" ht="12.75">
+    <row r="709" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -19676,7 +19720,7 @@
       <c r="X709" s="1"/>
       <c r="Y709" s="1"/>
     </row>
-    <row r="710" spans="1:25" ht="12.75">
+    <row r="710" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -19703,7 +19747,7 @@
       <c r="X710" s="1"/>
       <c r="Y710" s="1"/>
     </row>
-    <row r="711" spans="1:25" ht="12.75">
+    <row r="711" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -19730,7 +19774,7 @@
       <c r="X711" s="1"/>
       <c r="Y711" s="1"/>
     </row>
-    <row r="712" spans="1:25" ht="12.75">
+    <row r="712" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -19757,7 +19801,7 @@
       <c r="X712" s="1"/>
       <c r="Y712" s="1"/>
     </row>
-    <row r="713" spans="1:25" ht="12.75">
+    <row r="713" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -19784,7 +19828,7 @@
       <c r="X713" s="1"/>
       <c r="Y713" s="1"/>
     </row>
-    <row r="714" spans="1:25" ht="12.75">
+    <row r="714" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -19811,7 +19855,7 @@
       <c r="X714" s="1"/>
       <c r="Y714" s="1"/>
     </row>
-    <row r="715" spans="1:25" ht="12.75">
+    <row r="715" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -19838,7 +19882,7 @@
       <c r="X715" s="1"/>
       <c r="Y715" s="1"/>
     </row>
-    <row r="716" spans="1:25" ht="12.75">
+    <row r="716" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -19865,7 +19909,7 @@
       <c r="X716" s="1"/>
       <c r="Y716" s="1"/>
     </row>
-    <row r="717" spans="1:25" ht="12.75">
+    <row r="717" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -19892,7 +19936,7 @@
       <c r="X717" s="1"/>
       <c r="Y717" s="1"/>
     </row>
-    <row r="718" spans="1:25" ht="12.75">
+    <row r="718" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -19919,7 +19963,7 @@
       <c r="X718" s="1"/>
       <c r="Y718" s="1"/>
     </row>
-    <row r="719" spans="1:25" ht="12.75">
+    <row r="719" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -19946,7 +19990,7 @@
       <c r="X719" s="1"/>
       <c r="Y719" s="1"/>
     </row>
-    <row r="720" spans="1:25" ht="12.75">
+    <row r="720" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -19973,7 +20017,7 @@
       <c r="X720" s="1"/>
       <c r="Y720" s="1"/>
     </row>
-    <row r="721" spans="1:25" ht="12.75">
+    <row r="721" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -20000,7 +20044,7 @@
       <c r="X721" s="1"/>
       <c r="Y721" s="1"/>
     </row>
-    <row r="722" spans="1:25" ht="12.75">
+    <row r="722" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -20027,7 +20071,7 @@
       <c r="X722" s="1"/>
       <c r="Y722" s="1"/>
     </row>
-    <row r="723" spans="1:25" ht="12.75">
+    <row r="723" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -20054,7 +20098,7 @@
       <c r="X723" s="1"/>
       <c r="Y723" s="1"/>
     </row>
-    <row r="724" spans="1:25" ht="12.75">
+    <row r="724" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -20081,7 +20125,7 @@
       <c r="X724" s="1"/>
       <c r="Y724" s="1"/>
     </row>
-    <row r="725" spans="1:25" ht="12.75">
+    <row r="725" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -20108,7 +20152,7 @@
       <c r="X725" s="1"/>
       <c r="Y725" s="1"/>
     </row>
-    <row r="726" spans="1:25" ht="12.75">
+    <row r="726" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -20135,7 +20179,7 @@
       <c r="X726" s="1"/>
       <c r="Y726" s="1"/>
     </row>
-    <row r="727" spans="1:25" ht="12.75">
+    <row r="727" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -20162,7 +20206,7 @@
       <c r="X727" s="1"/>
       <c r="Y727" s="1"/>
     </row>
-    <row r="728" spans="1:25" ht="12.75">
+    <row r="728" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -20189,7 +20233,7 @@
       <c r="X728" s="1"/>
       <c r="Y728" s="1"/>
     </row>
-    <row r="729" spans="1:25" ht="12.75">
+    <row r="729" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -20216,7 +20260,7 @@
       <c r="X729" s="1"/>
       <c r="Y729" s="1"/>
     </row>
-    <row r="730" spans="1:25" ht="12.75">
+    <row r="730" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -20243,7 +20287,7 @@
       <c r="X730" s="1"/>
       <c r="Y730" s="1"/>
     </row>
-    <row r="731" spans="1:25" ht="12.75">
+    <row r="731" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -20270,7 +20314,7 @@
       <c r="X731" s="1"/>
       <c r="Y731" s="1"/>
     </row>
-    <row r="732" spans="1:25" ht="12.75">
+    <row r="732" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -20297,7 +20341,7 @@
       <c r="X732" s="1"/>
       <c r="Y732" s="1"/>
     </row>
-    <row r="733" spans="1:25" ht="12.75">
+    <row r="733" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -20324,7 +20368,7 @@
       <c r="X733" s="1"/>
       <c r="Y733" s="1"/>
     </row>
-    <row r="734" spans="1:25" ht="12.75">
+    <row r="734" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -20351,7 +20395,7 @@
       <c r="X734" s="1"/>
       <c r="Y734" s="1"/>
     </row>
-    <row r="735" spans="1:25" ht="12.75">
+    <row r="735" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -20378,7 +20422,7 @@
       <c r="X735" s="1"/>
       <c r="Y735" s="1"/>
     </row>
-    <row r="736" spans="1:25" ht="12.75">
+    <row r="736" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -20405,7 +20449,7 @@
       <c r="X736" s="1"/>
       <c r="Y736" s="1"/>
     </row>
-    <row r="737" spans="1:25" ht="12.75">
+    <row r="737" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -20432,7 +20476,7 @@
       <c r="X737" s="1"/>
       <c r="Y737" s="1"/>
     </row>
-    <row r="738" spans="1:25" ht="12.75">
+    <row r="738" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -20459,7 +20503,7 @@
       <c r="X738" s="1"/>
       <c r="Y738" s="1"/>
     </row>
-    <row r="739" spans="1:25" ht="12.75">
+    <row r="739" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -20486,7 +20530,7 @@
       <c r="X739" s="1"/>
       <c r="Y739" s="1"/>
     </row>
-    <row r="740" spans="1:25" ht="12.75">
+    <row r="740" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -20513,7 +20557,7 @@
       <c r="X740" s="1"/>
       <c r="Y740" s="1"/>
     </row>
-    <row r="741" spans="1:25" ht="12.75">
+    <row r="741" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -20540,7 +20584,7 @@
       <c r="X741" s="1"/>
       <c r="Y741" s="1"/>
     </row>
-    <row r="742" spans="1:25" ht="12.75">
+    <row r="742" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -20567,7 +20611,7 @@
       <c r="X742" s="1"/>
       <c r="Y742" s="1"/>
     </row>
-    <row r="743" spans="1:25" ht="12.75">
+    <row r="743" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -20594,7 +20638,7 @@
       <c r="X743" s="1"/>
       <c r="Y743" s="1"/>
     </row>
-    <row r="744" spans="1:25" ht="12.75">
+    <row r="744" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -20621,7 +20665,7 @@
       <c r="X744" s="1"/>
       <c r="Y744" s="1"/>
     </row>
-    <row r="745" spans="1:25" ht="12.75">
+    <row r="745" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -20648,7 +20692,7 @@
       <c r="X745" s="1"/>
       <c r="Y745" s="1"/>
     </row>
-    <row r="746" spans="1:25" ht="12.75">
+    <row r="746" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -20675,7 +20719,7 @@
       <c r="X746" s="1"/>
       <c r="Y746" s="1"/>
     </row>
-    <row r="747" spans="1:25" ht="12.75">
+    <row r="747" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -20702,7 +20746,7 @@
       <c r="X747" s="1"/>
       <c r="Y747" s="1"/>
     </row>
-    <row r="748" spans="1:25" ht="12.75">
+    <row r="748" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -20729,7 +20773,7 @@
       <c r="X748" s="1"/>
       <c r="Y748" s="1"/>
     </row>
-    <row r="749" spans="1:25" ht="12.75">
+    <row r="749" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -20756,7 +20800,7 @@
       <c r="X749" s="1"/>
       <c r="Y749" s="1"/>
     </row>
-    <row r="750" spans="1:25" ht="12.75">
+    <row r="750" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -20783,7 +20827,7 @@
       <c r="X750" s="1"/>
       <c r="Y750" s="1"/>
     </row>
-    <row r="751" spans="1:25" ht="12.75">
+    <row r="751" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -20810,7 +20854,7 @@
       <c r="X751" s="1"/>
       <c r="Y751" s="1"/>
     </row>
-    <row r="752" spans="1:25" ht="12.75">
+    <row r="752" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -20837,7 +20881,7 @@
       <c r="X752" s="1"/>
       <c r="Y752" s="1"/>
     </row>
-    <row r="753" spans="1:25" ht="12.75">
+    <row r="753" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -20864,7 +20908,7 @@
       <c r="X753" s="1"/>
       <c r="Y753" s="1"/>
     </row>
-    <row r="754" spans="1:25" ht="12.75">
+    <row r="754" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -20891,7 +20935,7 @@
       <c r="X754" s="1"/>
       <c r="Y754" s="1"/>
     </row>
-    <row r="755" spans="1:25" ht="12.75">
+    <row r="755" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -20918,7 +20962,7 @@
       <c r="X755" s="1"/>
       <c r="Y755" s="1"/>
     </row>
-    <row r="756" spans="1:25" ht="12.75">
+    <row r="756" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -20945,7 +20989,7 @@
       <c r="X756" s="1"/>
       <c r="Y756" s="1"/>
     </row>
-    <row r="757" spans="1:25" ht="12.75">
+    <row r="757" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -20972,7 +21016,7 @@
       <c r="X757" s="1"/>
       <c r="Y757" s="1"/>
     </row>
-    <row r="758" spans="1:25" ht="12.75">
+    <row r="758" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -20999,7 +21043,7 @@
       <c r="X758" s="1"/>
       <c r="Y758" s="1"/>
     </row>
-    <row r="759" spans="1:25" ht="12.75">
+    <row r="759" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -21026,7 +21070,7 @@
       <c r="X759" s="1"/>
       <c r="Y759" s="1"/>
     </row>
-    <row r="760" spans="1:25" ht="12.75">
+    <row r="760" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -21053,7 +21097,7 @@
       <c r="X760" s="1"/>
       <c r="Y760" s="1"/>
     </row>
-    <row r="761" spans="1:25" ht="12.75">
+    <row r="761" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -21080,7 +21124,7 @@
       <c r="X761" s="1"/>
       <c r="Y761" s="1"/>
     </row>
-    <row r="762" spans="1:25" ht="12.75">
+    <row r="762" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -21107,7 +21151,7 @@
       <c r="X762" s="1"/>
       <c r="Y762" s="1"/>
     </row>
-    <row r="763" spans="1:25" ht="12.75">
+    <row r="763" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -21134,7 +21178,7 @@
       <c r="X763" s="1"/>
       <c r="Y763" s="1"/>
     </row>
-    <row r="764" spans="1:25" ht="12.75">
+    <row r="764" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -21161,7 +21205,7 @@
       <c r="X764" s="1"/>
       <c r="Y764" s="1"/>
     </row>
-    <row r="765" spans="1:25" ht="12.75">
+    <row r="765" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -21188,7 +21232,7 @@
       <c r="X765" s="1"/>
       <c r="Y765" s="1"/>
     </row>
-    <row r="766" spans="1:25" ht="12.75">
+    <row r="766" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -21215,7 +21259,7 @@
       <c r="X766" s="1"/>
       <c r="Y766" s="1"/>
     </row>
-    <row r="767" spans="1:25" ht="12.75">
+    <row r="767" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -21242,7 +21286,7 @@
       <c r="X767" s="1"/>
       <c r="Y767" s="1"/>
     </row>
-    <row r="768" spans="1:25" ht="12.75">
+    <row r="768" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -21269,7 +21313,7 @@
       <c r="X768" s="1"/>
       <c r="Y768" s="1"/>
     </row>
-    <row r="769" spans="1:25" ht="12.75">
+    <row r="769" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -21296,7 +21340,7 @@
       <c r="X769" s="1"/>
       <c r="Y769" s="1"/>
     </row>
-    <row r="770" spans="1:25" ht="12.75">
+    <row r="770" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -21323,7 +21367,7 @@
       <c r="X770" s="1"/>
       <c r="Y770" s="1"/>
     </row>
-    <row r="771" spans="1:25" ht="12.75">
+    <row r="771" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -21350,7 +21394,7 @@
       <c r="X771" s="1"/>
       <c r="Y771" s="1"/>
     </row>
-    <row r="772" spans="1:25" ht="12.75">
+    <row r="772" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -21377,7 +21421,7 @@
       <c r="X772" s="1"/>
       <c r="Y772" s="1"/>
     </row>
-    <row r="773" spans="1:25" ht="12.75">
+    <row r="773" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -21404,7 +21448,7 @@
       <c r="X773" s="1"/>
       <c r="Y773" s="1"/>
     </row>
-    <row r="774" spans="1:25" ht="12.75">
+    <row r="774" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -21431,7 +21475,7 @@
       <c r="X774" s="1"/>
       <c r="Y774" s="1"/>
     </row>
-    <row r="775" spans="1:25" ht="12.75">
+    <row r="775" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -21458,7 +21502,7 @@
       <c r="X775" s="1"/>
       <c r="Y775" s="1"/>
     </row>
-    <row r="776" spans="1:25" ht="12.75">
+    <row r="776" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -21485,7 +21529,7 @@
       <c r="X776" s="1"/>
       <c r="Y776" s="1"/>
     </row>
-    <row r="777" spans="1:25" ht="12.75">
+    <row r="777" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -21512,7 +21556,7 @@
       <c r="X777" s="1"/>
       <c r="Y777" s="1"/>
     </row>
-    <row r="778" spans="1:25" ht="12.75">
+    <row r="778" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -21539,7 +21583,7 @@
       <c r="X778" s="1"/>
       <c r="Y778" s="1"/>
     </row>
-    <row r="779" spans="1:25" ht="12.75">
+    <row r="779" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -21566,7 +21610,7 @@
       <c r="X779" s="1"/>
       <c r="Y779" s="1"/>
     </row>
-    <row r="780" spans="1:25" ht="12.75">
+    <row r="780" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -21593,7 +21637,7 @@
       <c r="X780" s="1"/>
       <c r="Y780" s="1"/>
     </row>
-    <row r="781" spans="1:25" ht="12.75">
+    <row r="781" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -21620,7 +21664,7 @@
       <c r="X781" s="1"/>
       <c r="Y781" s="1"/>
     </row>
-    <row r="782" spans="1:25" ht="12.75">
+    <row r="782" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -21647,7 +21691,7 @@
       <c r="X782" s="1"/>
       <c r="Y782" s="1"/>
     </row>
-    <row r="783" spans="1:25" ht="12.75">
+    <row r="783" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -21674,7 +21718,7 @@
       <c r="X783" s="1"/>
       <c r="Y783" s="1"/>
     </row>
-    <row r="784" spans="1:25" ht="12.75">
+    <row r="784" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -21701,7 +21745,7 @@
       <c r="X784" s="1"/>
       <c r="Y784" s="1"/>
     </row>
-    <row r="785" spans="1:25" ht="12.75">
+    <row r="785" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -21728,7 +21772,7 @@
       <c r="X785" s="1"/>
       <c r="Y785" s="1"/>
     </row>
-    <row r="786" spans="1:25" ht="12.75">
+    <row r="786" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -21755,7 +21799,7 @@
       <c r="X786" s="1"/>
       <c r="Y786" s="1"/>
     </row>
-    <row r="787" spans="1:25" ht="12.75">
+    <row r="787" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -21782,7 +21826,7 @@
       <c r="X787" s="1"/>
       <c r="Y787" s="1"/>
     </row>
-    <row r="788" spans="1:25" ht="12.75">
+    <row r="788" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -21809,7 +21853,7 @@
       <c r="X788" s="1"/>
       <c r="Y788" s="1"/>
     </row>
-    <row r="789" spans="1:25" ht="12.75">
+    <row r="789" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -21836,7 +21880,7 @@
       <c r="X789" s="1"/>
       <c r="Y789" s="1"/>
     </row>
-    <row r="790" spans="1:25" ht="12.75">
+    <row r="790" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -21863,7 +21907,7 @@
       <c r="X790" s="1"/>
       <c r="Y790" s="1"/>
     </row>
-    <row r="791" spans="1:25" ht="12.75">
+    <row r="791" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -21890,7 +21934,7 @@
       <c r="X791" s="1"/>
       <c r="Y791" s="1"/>
     </row>
-    <row r="792" spans="1:25" ht="12.75">
+    <row r="792" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -21917,7 +21961,7 @@
       <c r="X792" s="1"/>
       <c r="Y792" s="1"/>
     </row>
-    <row r="793" spans="1:25" ht="12.75">
+    <row r="793" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -21944,7 +21988,7 @@
       <c r="X793" s="1"/>
       <c r="Y793" s="1"/>
     </row>
-    <row r="794" spans="1:25" ht="12.75">
+    <row r="794" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -21971,7 +22015,7 @@
       <c r="X794" s="1"/>
       <c r="Y794" s="1"/>
     </row>
-    <row r="795" spans="1:25" ht="12.75">
+    <row r="795" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -21998,7 +22042,7 @@
       <c r="X795" s="1"/>
       <c r="Y795" s="1"/>
     </row>
-    <row r="796" spans="1:25" ht="12.75">
+    <row r="796" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -22025,7 +22069,7 @@
       <c r="X796" s="1"/>
       <c r="Y796" s="1"/>
     </row>
-    <row r="797" spans="1:25" ht="12.75">
+    <row r="797" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -22052,7 +22096,7 @@
       <c r="X797" s="1"/>
       <c r="Y797" s="1"/>
     </row>
-    <row r="798" spans="1:25" ht="12.75">
+    <row r="798" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -22079,7 +22123,7 @@
       <c r="X798" s="1"/>
       <c r="Y798" s="1"/>
     </row>
-    <row r="799" spans="1:25" ht="12.75">
+    <row r="799" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -22106,7 +22150,7 @@
       <c r="X799" s="1"/>
       <c r="Y799" s="1"/>
     </row>
-    <row r="800" spans="1:25" ht="12.75">
+    <row r="800" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -22133,7 +22177,7 @@
       <c r="X800" s="1"/>
       <c r="Y800" s="1"/>
     </row>
-    <row r="801" spans="1:25" ht="12.75">
+    <row r="801" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -22160,7 +22204,7 @@
       <c r="X801" s="1"/>
       <c r="Y801" s="1"/>
     </row>
-    <row r="802" spans="1:25" ht="12.75">
+    <row r="802" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -22187,7 +22231,7 @@
       <c r="X802" s="1"/>
       <c r="Y802" s="1"/>
     </row>
-    <row r="803" spans="1:25" ht="12.75">
+    <row r="803" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -22214,7 +22258,7 @@
       <c r="X803" s="1"/>
       <c r="Y803" s="1"/>
     </row>
-    <row r="804" spans="1:25" ht="12.75">
+    <row r="804" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -22241,7 +22285,7 @@
       <c r="X804" s="1"/>
       <c r="Y804" s="1"/>
     </row>
-    <row r="805" spans="1:25" ht="12.75">
+    <row r="805" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -22268,7 +22312,7 @@
       <c r="X805" s="1"/>
       <c r="Y805" s="1"/>
     </row>
-    <row r="806" spans="1:25" ht="12.75">
+    <row r="806" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -22295,7 +22339,7 @@
       <c r="X806" s="1"/>
       <c r="Y806" s="1"/>
     </row>
-    <row r="807" spans="1:25" ht="12.75">
+    <row r="807" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -22322,7 +22366,7 @@
       <c r="X807" s="1"/>
       <c r="Y807" s="1"/>
     </row>
-    <row r="808" spans="1:25" ht="12.75">
+    <row r="808" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -22349,7 +22393,7 @@
       <c r="X808" s="1"/>
       <c r="Y808" s="1"/>
     </row>
-    <row r="809" spans="1:25" ht="12.75">
+    <row r="809" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -22376,7 +22420,7 @@
       <c r="X809" s="1"/>
       <c r="Y809" s="1"/>
     </row>
-    <row r="810" spans="1:25" ht="12.75">
+    <row r="810" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -22403,7 +22447,7 @@
       <c r="X810" s="1"/>
       <c r="Y810" s="1"/>
     </row>
-    <row r="811" spans="1:25" ht="12.75">
+    <row r="811" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -22430,7 +22474,7 @@
       <c r="X811" s="1"/>
       <c r="Y811" s="1"/>
     </row>
-    <row r="812" spans="1:25" ht="12.75">
+    <row r="812" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -22457,7 +22501,7 @@
       <c r="X812" s="1"/>
       <c r="Y812" s="1"/>
     </row>
-    <row r="813" spans="1:25" ht="12.75">
+    <row r="813" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -22484,7 +22528,7 @@
       <c r="X813" s="1"/>
       <c r="Y813" s="1"/>
     </row>
-    <row r="814" spans="1:25" ht="12.75">
+    <row r="814" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -22511,7 +22555,7 @@
       <c r="X814" s="1"/>
       <c r="Y814" s="1"/>
     </row>
-    <row r="815" spans="1:25" ht="12.75">
+    <row r="815" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -22538,7 +22582,7 @@
       <c r="X815" s="1"/>
       <c r="Y815" s="1"/>
     </row>
-    <row r="816" spans="1:25" ht="12.75">
+    <row r="816" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -22565,7 +22609,7 @@
       <c r="X816" s="1"/>
       <c r="Y816" s="1"/>
     </row>
-    <row r="817" spans="1:25" ht="12.75">
+    <row r="817" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -22592,7 +22636,7 @@
       <c r="X817" s="1"/>
       <c r="Y817" s="1"/>
     </row>
-    <row r="818" spans="1:25" ht="12.75">
+    <row r="818" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -22619,7 +22663,7 @@
       <c r="X818" s="1"/>
       <c r="Y818" s="1"/>
     </row>
-    <row r="819" spans="1:25" ht="12.75">
+    <row r="819" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -22646,7 +22690,7 @@
       <c r="X819" s="1"/>
       <c r="Y819" s="1"/>
     </row>
-    <row r="820" spans="1:25" ht="12.75">
+    <row r="820" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -22673,7 +22717,7 @@
       <c r="X820" s="1"/>
       <c r="Y820" s="1"/>
     </row>
-    <row r="821" spans="1:25" ht="12.75">
+    <row r="821" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -22700,7 +22744,7 @@
       <c r="X821" s="1"/>
       <c r="Y821" s="1"/>
     </row>
-    <row r="822" spans="1:25" ht="12.75">
+    <row r="822" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -22727,7 +22771,7 @@
       <c r="X822" s="1"/>
       <c r="Y822" s="1"/>
     </row>
-    <row r="823" spans="1:25" ht="12.75">
+    <row r="823" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -22754,7 +22798,7 @@
       <c r="X823" s="1"/>
       <c r="Y823" s="1"/>
     </row>
-    <row r="824" spans="1:25" ht="12.75">
+    <row r="824" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -22781,7 +22825,7 @@
       <c r="X824" s="1"/>
       <c r="Y824" s="1"/>
     </row>
-    <row r="825" spans="1:25" ht="12.75">
+    <row r="825" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -22808,7 +22852,7 @@
       <c r="X825" s="1"/>
       <c r="Y825" s="1"/>
     </row>
-    <row r="826" spans="1:25" ht="12.75">
+    <row r="826" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -22835,7 +22879,7 @@
       <c r="X826" s="1"/>
       <c r="Y826" s="1"/>
     </row>
-    <row r="827" spans="1:25" ht="12.75">
+    <row r="827" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -22862,7 +22906,7 @@
       <c r="X827" s="1"/>
       <c r="Y827" s="1"/>
     </row>
-    <row r="828" spans="1:25" ht="12.75">
+    <row r="828" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -22889,7 +22933,7 @@
       <c r="X828" s="1"/>
       <c r="Y828" s="1"/>
     </row>
-    <row r="829" spans="1:25" ht="12.75">
+    <row r="829" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -22916,7 +22960,7 @@
       <c r="X829" s="1"/>
       <c r="Y829" s="1"/>
     </row>
-    <row r="830" spans="1:25" ht="12.75">
+    <row r="830" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -22943,7 +22987,7 @@
       <c r="X830" s="1"/>
       <c r="Y830" s="1"/>
     </row>
-    <row r="831" spans="1:25" ht="12.75">
+    <row r="831" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -22970,7 +23014,7 @@
       <c r="X831" s="1"/>
       <c r="Y831" s="1"/>
     </row>
-    <row r="832" spans="1:25" ht="12.75">
+    <row r="832" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -22997,7 +23041,7 @@
       <c r="X832" s="1"/>
       <c r="Y832" s="1"/>
     </row>
-    <row r="833" spans="1:25" ht="12.75">
+    <row r="833" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -23024,7 +23068,7 @@
       <c r="X833" s="1"/>
       <c r="Y833" s="1"/>
     </row>
-    <row r="834" spans="1:25" ht="12.75">
+    <row r="834" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -23051,7 +23095,7 @@
       <c r="X834" s="1"/>
       <c r="Y834" s="1"/>
     </row>
-    <row r="835" spans="1:25" ht="12.75">
+    <row r="835" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -23078,7 +23122,7 @@
       <c r="X835" s="1"/>
       <c r="Y835" s="1"/>
     </row>
-    <row r="836" spans="1:25" ht="12.75">
+    <row r="836" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -23105,7 +23149,7 @@
       <c r="X836" s="1"/>
       <c r="Y836" s="1"/>
     </row>
-    <row r="837" spans="1:25" ht="12.75">
+    <row r="837" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -23132,7 +23176,7 @@
       <c r="X837" s="1"/>
       <c r="Y837" s="1"/>
     </row>
-    <row r="838" spans="1:25" ht="12.75">
+    <row r="838" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -23159,7 +23203,7 @@
       <c r="X838" s="1"/>
       <c r="Y838" s="1"/>
     </row>
-    <row r="839" spans="1:25" ht="12.75">
+    <row r="839" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -23186,7 +23230,7 @@
       <c r="X839" s="1"/>
       <c r="Y839" s="1"/>
     </row>
-    <row r="840" spans="1:25" ht="12.75">
+    <row r="840" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -23213,7 +23257,7 @@
       <c r="X840" s="1"/>
       <c r="Y840" s="1"/>
     </row>
-    <row r="841" spans="1:25" ht="12.75">
+    <row r="841" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -23240,7 +23284,7 @@
       <c r="X841" s="1"/>
       <c r="Y841" s="1"/>
     </row>
-    <row r="842" spans="1:25" ht="12.75">
+    <row r="842" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -23267,7 +23311,7 @@
       <c r="X842" s="1"/>
       <c r="Y842" s="1"/>
     </row>
-    <row r="843" spans="1:25" ht="12.75">
+    <row r="843" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -23294,7 +23338,7 @@
       <c r="X843" s="1"/>
       <c r="Y843" s="1"/>
     </row>
-    <row r="844" spans="1:25" ht="12.75">
+    <row r="844" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -23321,7 +23365,7 @@
       <c r="X844" s="1"/>
       <c r="Y844" s="1"/>
     </row>
-    <row r="845" spans="1:25" ht="12.75">
+    <row r="845" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -23348,7 +23392,7 @@
       <c r="X845" s="1"/>
       <c r="Y845" s="1"/>
     </row>
-    <row r="846" spans="1:25" ht="12.75">
+    <row r="846" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -23375,7 +23419,7 @@
       <c r="X846" s="1"/>
       <c r="Y846" s="1"/>
     </row>
-    <row r="847" spans="1:25" ht="12.75">
+    <row r="847" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -23402,7 +23446,7 @@
       <c r="X847" s="1"/>
       <c r="Y847" s="1"/>
     </row>
-    <row r="848" spans="1:25" ht="12.75">
+    <row r="848" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -23429,7 +23473,7 @@
       <c r="X848" s="1"/>
       <c r="Y848" s="1"/>
     </row>
-    <row r="849" spans="1:25" ht="12.75">
+    <row r="849" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -23456,7 +23500,7 @@
       <c r="X849" s="1"/>
       <c r="Y849" s="1"/>
     </row>
-    <row r="850" spans="1:25" ht="12.75">
+    <row r="850" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -23483,7 +23527,7 @@
       <c r="X850" s="1"/>
       <c r="Y850" s="1"/>
     </row>
-    <row r="851" spans="1:25" ht="12.75">
+    <row r="851" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -23510,7 +23554,7 @@
       <c r="X851" s="1"/>
       <c r="Y851" s="1"/>
     </row>
-    <row r="852" spans="1:25" ht="12.75">
+    <row r="852" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -23537,7 +23581,7 @@
       <c r="X852" s="1"/>
       <c r="Y852" s="1"/>
     </row>
-    <row r="853" spans="1:25" ht="12.75">
+    <row r="853" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -23564,7 +23608,7 @@
       <c r="X853" s="1"/>
       <c r="Y853" s="1"/>
     </row>
-    <row r="854" spans="1:25" ht="12.75">
+    <row r="854" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -23591,7 +23635,7 @@
       <c r="X854" s="1"/>
       <c r="Y854" s="1"/>
     </row>
-    <row r="855" spans="1:25" ht="12.75">
+    <row r="855" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -23618,7 +23662,7 @@
       <c r="X855" s="1"/>
       <c r="Y855" s="1"/>
     </row>
-    <row r="856" spans="1:25" ht="12.75">
+    <row r="856" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -23645,7 +23689,7 @@
       <c r="X856" s="1"/>
       <c r="Y856" s="1"/>
     </row>
-    <row r="857" spans="1:25" ht="12.75">
+    <row r="857" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -23672,7 +23716,7 @@
       <c r="X857" s="1"/>
       <c r="Y857" s="1"/>
     </row>
-    <row r="858" spans="1:25" ht="12.75">
+    <row r="858" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -23699,7 +23743,7 @@
       <c r="X858" s="1"/>
       <c r="Y858" s="1"/>
     </row>
-    <row r="859" spans="1:25" ht="12.75">
+    <row r="859" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -23726,7 +23770,7 @@
       <c r="X859" s="1"/>
       <c r="Y859" s="1"/>
     </row>
-    <row r="860" spans="1:25" ht="12.75">
+    <row r="860" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -23753,7 +23797,7 @@
       <c r="X860" s="1"/>
       <c r="Y860" s="1"/>
     </row>
-    <row r="861" spans="1:25" ht="12.75">
+    <row r="861" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -23780,7 +23824,7 @@
       <c r="X861" s="1"/>
       <c r="Y861" s="1"/>
     </row>
-    <row r="862" spans="1:25" ht="12.75">
+    <row r="862" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -23807,7 +23851,7 @@
       <c r="X862" s="1"/>
       <c r="Y862" s="1"/>
     </row>
-    <row r="863" spans="1:25" ht="12.75">
+    <row r="863" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -23834,7 +23878,7 @@
       <c r="X863" s="1"/>
       <c r="Y863" s="1"/>
     </row>
-    <row r="864" spans="1:25" ht="12.75">
+    <row r="864" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -23861,7 +23905,7 @@
       <c r="X864" s="1"/>
       <c r="Y864" s="1"/>
     </row>
-    <row r="865" spans="1:25" ht="12.75">
+    <row r="865" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -23888,7 +23932,7 @@
       <c r="X865" s="1"/>
       <c r="Y865" s="1"/>
     </row>
-    <row r="866" spans="1:25" ht="12.75">
+    <row r="866" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -23915,7 +23959,7 @@
       <c r="X866" s="1"/>
       <c r="Y866" s="1"/>
     </row>
-    <row r="867" spans="1:25" ht="12.75">
+    <row r="867" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -23942,7 +23986,7 @@
       <c r="X867" s="1"/>
       <c r="Y867" s="1"/>
     </row>
-    <row r="868" spans="1:25" ht="12.75">
+    <row r="868" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -23969,7 +24013,7 @@
       <c r="X868" s="1"/>
       <c r="Y868" s="1"/>
     </row>
-    <row r="869" spans="1:25" ht="12.75">
+    <row r="869" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -23996,7 +24040,7 @@
       <c r="X869" s="1"/>
       <c r="Y869" s="1"/>
     </row>
-    <row r="870" spans="1:25" ht="12.75">
+    <row r="870" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -24023,7 +24067,7 @@
       <c r="X870" s="1"/>
       <c r="Y870" s="1"/>
     </row>
-    <row r="871" spans="1:25" ht="12.75">
+    <row r="871" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -24050,7 +24094,7 @@
       <c r="X871" s="1"/>
       <c r="Y871" s="1"/>
     </row>
-    <row r="872" spans="1:25" ht="12.75">
+    <row r="872" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -24077,7 +24121,7 @@
       <c r="X872" s="1"/>
       <c r="Y872" s="1"/>
     </row>
-    <row r="873" spans="1:25" ht="12.75">
+    <row r="873" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -24104,7 +24148,7 @@
       <c r="X873" s="1"/>
       <c r="Y873" s="1"/>
     </row>
-    <row r="874" spans="1:25" ht="12.75">
+    <row r="874" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -24131,7 +24175,7 @@
       <c r="X874" s="1"/>
       <c r="Y874" s="1"/>
     </row>
-    <row r="875" spans="1:25" ht="12.75">
+    <row r="875" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -24158,7 +24202,7 @@
       <c r="X875" s="1"/>
       <c r="Y875" s="1"/>
     </row>
-    <row r="876" spans="1:25" ht="12.75">
+    <row r="876" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -24185,7 +24229,7 @@
       <c r="X876" s="1"/>
       <c r="Y876" s="1"/>
     </row>
-    <row r="877" spans="1:25" ht="12.75">
+    <row r="877" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -24212,7 +24256,7 @@
       <c r="X877" s="1"/>
       <c r="Y877" s="1"/>
     </row>
-    <row r="878" spans="1:25" ht="12.75">
+    <row r="878" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -24239,7 +24283,7 @@
       <c r="X878" s="1"/>
       <c r="Y878" s="1"/>
     </row>
-    <row r="879" spans="1:25" ht="12.75">
+    <row r="879" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -24266,7 +24310,7 @@
       <c r="X879" s="1"/>
       <c r="Y879" s="1"/>
     </row>
-    <row r="880" spans="1:25" ht="12.75">
+    <row r="880" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -24293,7 +24337,7 @@
       <c r="X880" s="1"/>
       <c r="Y880" s="1"/>
     </row>
-    <row r="881" spans="1:25" ht="12.75">
+    <row r="881" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -24320,7 +24364,7 @@
       <c r="X881" s="1"/>
       <c r="Y881" s="1"/>
     </row>
-    <row r="882" spans="1:25" ht="12.75">
+    <row r="882" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -24347,7 +24391,7 @@
       <c r="X882" s="1"/>
       <c r="Y882" s="1"/>
     </row>
-    <row r="883" spans="1:25" ht="12.75">
+    <row r="883" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -24374,7 +24418,7 @@
       <c r="X883" s="1"/>
       <c r="Y883" s="1"/>
     </row>
-    <row r="884" spans="1:25" ht="12.75">
+    <row r="884" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -24401,7 +24445,7 @@
       <c r="X884" s="1"/>
       <c r="Y884" s="1"/>
     </row>
-    <row r="885" spans="1:25" ht="12.75">
+    <row r="885" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -24428,7 +24472,7 @@
       <c r="X885" s="1"/>
       <c r="Y885" s="1"/>
     </row>
-    <row r="886" spans="1:25" ht="12.75">
+    <row r="886" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -24455,7 +24499,7 @@
       <c r="X886" s="1"/>
       <c r="Y886" s="1"/>
     </row>
-    <row r="887" spans="1:25" ht="12.75">
+    <row r="887" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -24482,7 +24526,7 @@
       <c r="X887" s="1"/>
       <c r="Y887" s="1"/>
     </row>
-    <row r="888" spans="1:25" ht="12.75">
+    <row r="888" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -24509,7 +24553,7 @@
       <c r="X888" s="1"/>
       <c r="Y888" s="1"/>
     </row>
-    <row r="889" spans="1:25" ht="12.75">
+    <row r="889" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -24536,7 +24580,7 @@
       <c r="X889" s="1"/>
       <c r="Y889" s="1"/>
     </row>
-    <row r="890" spans="1:25" ht="12.75">
+    <row r="890" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -24563,7 +24607,7 @@
       <c r="X890" s="1"/>
       <c r="Y890" s="1"/>
     </row>
-    <row r="891" spans="1:25" ht="12.75">
+    <row r="891" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -24590,7 +24634,7 @@
       <c r="X891" s="1"/>
       <c r="Y891" s="1"/>
     </row>
-    <row r="892" spans="1:25" ht="12.75">
+    <row r="892" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -24617,7 +24661,7 @@
       <c r="X892" s="1"/>
       <c r="Y892" s="1"/>
     </row>
-    <row r="893" spans="1:25" ht="12.75">
+    <row r="893" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -24644,7 +24688,7 @@
       <c r="X893" s="1"/>
       <c r="Y893" s="1"/>
     </row>
-    <row r="894" spans="1:25" ht="12.75">
+    <row r="894" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -24671,7 +24715,7 @@
       <c r="X894" s="1"/>
       <c r="Y894" s="1"/>
     </row>
-    <row r="895" spans="1:25" ht="12.75">
+    <row r="895" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -24698,7 +24742,7 @@
       <c r="X895" s="1"/>
       <c r="Y895" s="1"/>
     </row>
-    <row r="896" spans="1:25" ht="12.75">
+    <row r="896" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -24725,7 +24769,7 @@
       <c r="X896" s="1"/>
       <c r="Y896" s="1"/>
     </row>
-    <row r="897" spans="1:25" ht="12.75">
+    <row r="897" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -24752,7 +24796,7 @@
       <c r="X897" s="1"/>
       <c r="Y897" s="1"/>
     </row>
-    <row r="898" spans="1:25" ht="12.75">
+    <row r="898" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -24779,7 +24823,7 @@
       <c r="X898" s="1"/>
       <c r="Y898" s="1"/>
     </row>
-    <row r="899" spans="1:25" ht="12.75">
+    <row r="899" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -24806,7 +24850,7 @@
       <c r="X899" s="1"/>
       <c r="Y899" s="1"/>
     </row>
-    <row r="900" spans="1:25" ht="12.75">
+    <row r="900" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -24833,7 +24877,7 @@
       <c r="X900" s="1"/>
       <c r="Y900" s="1"/>
     </row>
-    <row r="901" spans="1:25" ht="12.75">
+    <row r="901" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -24860,7 +24904,7 @@
       <c r="X901" s="1"/>
       <c r="Y901" s="1"/>
     </row>
-    <row r="902" spans="1:25" ht="12.75">
+    <row r="902" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -24887,7 +24931,7 @@
       <c r="X902" s="1"/>
       <c r="Y902" s="1"/>
     </row>
-    <row r="903" spans="1:25" ht="12.75">
+    <row r="903" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -24914,7 +24958,7 @@
       <c r="X903" s="1"/>
       <c r="Y903" s="1"/>
     </row>
-    <row r="904" spans="1:25" ht="12.75">
+    <row r="904" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -24941,7 +24985,7 @@
       <c r="X904" s="1"/>
       <c r="Y904" s="1"/>
     </row>
-    <row r="905" spans="1:25" ht="12.75">
+    <row r="905" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -24968,7 +25012,7 @@
       <c r="X905" s="1"/>
       <c r="Y905" s="1"/>
     </row>
-    <row r="906" spans="1:25" ht="12.75">
+    <row r="906" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -24995,7 +25039,7 @@
       <c r="X906" s="1"/>
       <c r="Y906" s="1"/>
     </row>
-    <row r="907" spans="1:25" ht="12.75">
+    <row r="907" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -25022,7 +25066,7 @@
       <c r="X907" s="1"/>
       <c r="Y907" s="1"/>
     </row>
-    <row r="908" spans="1:25" ht="12.75">
+    <row r="908" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -25049,7 +25093,7 @@
       <c r="X908" s="1"/>
       <c r="Y908" s="1"/>
     </row>
-    <row r="909" spans="1:25" ht="12.75">
+    <row r="909" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -25076,7 +25120,7 @@
       <c r="X909" s="1"/>
       <c r="Y909" s="1"/>
     </row>
-    <row r="910" spans="1:25" ht="12.75">
+    <row r="910" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -25103,7 +25147,7 @@
       <c r="X910" s="1"/>
       <c r="Y910" s="1"/>
     </row>
-    <row r="911" spans="1:25" ht="12.75">
+    <row r="911" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -25130,7 +25174,7 @@
       <c r="X911" s="1"/>
       <c r="Y911" s="1"/>
     </row>
-    <row r="912" spans="1:25" ht="12.75">
+    <row r="912" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -25157,7 +25201,7 @@
       <c r="X912" s="1"/>
       <c r="Y912" s="1"/>
     </row>
-    <row r="913" spans="1:25" ht="12.75">
+    <row r="913" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -25184,7 +25228,7 @@
       <c r="X913" s="1"/>
       <c r="Y913" s="1"/>
     </row>
-    <row r="914" spans="1:25" ht="12.75">
+    <row r="914" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -25211,7 +25255,7 @@
       <c r="X914" s="1"/>
       <c r="Y914" s="1"/>
     </row>
-    <row r="915" spans="1:25" ht="12.75">
+    <row r="915" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -25238,7 +25282,7 @@
       <c r="X915" s="1"/>
       <c r="Y915" s="1"/>
     </row>
-    <row r="916" spans="1:25" ht="12.75">
+    <row r="916" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -25265,7 +25309,7 @@
       <c r="X916" s="1"/>
       <c r="Y916" s="1"/>
     </row>
-    <row r="917" spans="1:25" ht="12.75">
+    <row r="917" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -25292,7 +25336,7 @@
       <c r="X917" s="1"/>
       <c r="Y917" s="1"/>
     </row>
-    <row r="918" spans="1:25" ht="12.75">
+    <row r="918" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -25319,7 +25363,7 @@
       <c r="X918" s="1"/>
       <c r="Y918" s="1"/>
     </row>
-    <row r="919" spans="1:25" ht="12.75">
+    <row r="919" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -25346,7 +25390,7 @@
       <c r="X919" s="1"/>
       <c r="Y919" s="1"/>
     </row>
-    <row r="920" spans="1:25" ht="12.75">
+    <row r="920" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -25373,7 +25417,7 @@
       <c r="X920" s="1"/>
       <c r="Y920" s="1"/>
     </row>
-    <row r="921" spans="1:25" ht="12.75">
+    <row r="921" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -25400,7 +25444,7 @@
       <c r="X921" s="1"/>
       <c r="Y921" s="1"/>
     </row>
-    <row r="922" spans="1:25" ht="12.75">
+    <row r="922" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -25427,7 +25471,7 @@
       <c r="X922" s="1"/>
       <c r="Y922" s="1"/>
     </row>
-    <row r="923" spans="1:25" ht="12.75">
+    <row r="923" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -25454,7 +25498,7 @@
       <c r="X923" s="1"/>
       <c r="Y923" s="1"/>
     </row>
-    <row r="924" spans="1:25" ht="12.75">
+    <row r="924" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -25481,7 +25525,7 @@
       <c r="X924" s="1"/>
       <c r="Y924" s="1"/>
     </row>
-    <row r="925" spans="1:25" ht="12.75">
+    <row r="925" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -25508,7 +25552,7 @@
       <c r="X925" s="1"/>
       <c r="Y925" s="1"/>
     </row>
-    <row r="926" spans="1:25" ht="12.75">
+    <row r="926" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -25535,7 +25579,7 @@
       <c r="X926" s="1"/>
       <c r="Y926" s="1"/>
     </row>
-    <row r="927" spans="1:25" ht="12.75">
+    <row r="927" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -25562,7 +25606,7 @@
       <c r="X927" s="1"/>
       <c r="Y927" s="1"/>
     </row>
-    <row r="928" spans="1:25" ht="12.75">
+    <row r="928" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -25589,7 +25633,7 @@
       <c r="X928" s="1"/>
       <c r="Y928" s="1"/>
     </row>
-    <row r="929" spans="1:25" ht="12.75">
+    <row r="929" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -25616,7 +25660,7 @@
       <c r="X929" s="1"/>
       <c r="Y929" s="1"/>
     </row>
-    <row r="930" spans="1:25" ht="12.75">
+    <row r="930" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -25643,7 +25687,7 @@
       <c r="X930" s="1"/>
       <c r="Y930" s="1"/>
     </row>
-    <row r="931" spans="1:25" ht="12.75">
+    <row r="931" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -25670,7 +25714,7 @@
       <c r="X931" s="1"/>
       <c r="Y931" s="1"/>
     </row>
-    <row r="932" spans="1:25" ht="12.75">
+    <row r="932" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -25697,7 +25741,7 @@
       <c r="X932" s="1"/>
       <c r="Y932" s="1"/>
     </row>
-    <row r="933" spans="1:25" ht="12.75">
+    <row r="933" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -25724,7 +25768,7 @@
       <c r="X933" s="1"/>
       <c r="Y933" s="1"/>
     </row>
-    <row r="934" spans="1:25" ht="12.75">
+    <row r="934" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -25751,7 +25795,7 @@
       <c r="X934" s="1"/>
       <c r="Y934" s="1"/>
     </row>
-    <row r="935" spans="1:25" ht="12.75">
+    <row r="935" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -25778,7 +25822,7 @@
       <c r="X935" s="1"/>
       <c r="Y935" s="1"/>
     </row>
-    <row r="936" spans="1:25" ht="12.75">
+    <row r="936" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -25805,7 +25849,7 @@
       <c r="X936" s="1"/>
       <c r="Y936" s="1"/>
     </row>
-    <row r="937" spans="1:25" ht="12.75">
+    <row r="937" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -25832,7 +25876,7 @@
       <c r="X937" s="1"/>
       <c r="Y937" s="1"/>
     </row>
-    <row r="938" spans="1:25" ht="12.75">
+    <row r="938" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -25859,7 +25903,7 @@
       <c r="X938" s="1"/>
       <c r="Y938" s="1"/>
     </row>
-    <row r="939" spans="1:25" ht="12.75">
+    <row r="939" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -25886,7 +25930,7 @@
       <c r="X939" s="1"/>
       <c r="Y939" s="1"/>
     </row>
-    <row r="940" spans="1:25" ht="12.75">
+    <row r="940" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -25913,7 +25957,7 @@
       <c r="X940" s="1"/>
       <c r="Y940" s="1"/>
     </row>
-    <row r="941" spans="1:25" ht="12.75">
+    <row r="941" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -25940,7 +25984,7 @@
       <c r="X941" s="1"/>
       <c r="Y941" s="1"/>
     </row>
-    <row r="942" spans="1:25" ht="12.75">
+    <row r="942" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -25967,7 +26011,7 @@
       <c r="X942" s="1"/>
       <c r="Y942" s="1"/>
     </row>
-    <row r="943" spans="1:25" ht="12.75">
+    <row r="943" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -25994,7 +26038,7 @@
       <c r="X943" s="1"/>
       <c r="Y943" s="1"/>
     </row>
-    <row r="944" spans="1:25" ht="12.75">
+    <row r="944" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -26021,7 +26065,7 @@
       <c r="X944" s="1"/>
       <c r="Y944" s="1"/>
     </row>
-    <row r="945" spans="1:25" ht="12.75">
+    <row r="945" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -26048,7 +26092,7 @@
       <c r="X945" s="1"/>
       <c r="Y945" s="1"/>
     </row>
-    <row r="946" spans="1:25" ht="12.75">
+    <row r="946" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -26075,7 +26119,7 @@
       <c r="X946" s="1"/>
       <c r="Y946" s="1"/>
     </row>
-    <row r="947" spans="1:25" ht="12.75">
+    <row r="947" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -26102,7 +26146,7 @@
       <c r="X947" s="1"/>
       <c r="Y947" s="1"/>
     </row>
-    <row r="948" spans="1:25" ht="12.75">
+    <row r="948" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -26129,7 +26173,7 @@
       <c r="X948" s="1"/>
       <c r="Y948" s="1"/>
     </row>
-    <row r="949" spans="1:25" ht="12.75">
+    <row r="949" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -26156,7 +26200,7 @@
       <c r="X949" s="1"/>
       <c r="Y949" s="1"/>
     </row>
-    <row r="950" spans="1:25" ht="12.75">
+    <row r="950" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -26183,7 +26227,7 @@
       <c r="X950" s="1"/>
       <c r="Y950" s="1"/>
     </row>
-    <row r="951" spans="1:25" ht="12.75">
+    <row r="951" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -26210,7 +26254,7 @@
       <c r="X951" s="1"/>
       <c r="Y951" s="1"/>
     </row>
-    <row r="952" spans="1:25" ht="12.75">
+    <row r="952" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -26237,7 +26281,7 @@
       <c r="X952" s="1"/>
       <c r="Y952" s="1"/>
     </row>
-    <row r="953" spans="1:25" ht="12.75">
+    <row r="953" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -26264,7 +26308,7 @@
       <c r="X953" s="1"/>
       <c r="Y953" s="1"/>
     </row>
-    <row r="954" spans="1:25" ht="12.75">
+    <row r="954" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -26291,7 +26335,7 @@
       <c r="X954" s="1"/>
       <c r="Y954" s="1"/>
     </row>
-    <row r="955" spans="1:25" ht="12.75">
+    <row r="955" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -26318,7 +26362,7 @@
       <c r="X955" s="1"/>
       <c r="Y955" s="1"/>
     </row>
-    <row r="956" spans="1:25" ht="12.75">
+    <row r="956" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -26345,7 +26389,7 @@
       <c r="X956" s="1"/>
       <c r="Y956" s="1"/>
     </row>
-    <row r="957" spans="1:25" ht="12.75">
+    <row r="957" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -26372,7 +26416,7 @@
       <c r="X957" s="1"/>
       <c r="Y957" s="1"/>
     </row>
-    <row r="958" spans="1:25" ht="12.75">
+    <row r="958" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -26399,7 +26443,7 @@
       <c r="X958" s="1"/>
       <c r="Y958" s="1"/>
     </row>
-    <row r="959" spans="1:25" ht="12.75">
+    <row r="959" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -26426,7 +26470,7 @@
       <c r="X959" s="1"/>
       <c r="Y959" s="1"/>
     </row>
-    <row r="960" spans="1:25" ht="12.75">
+    <row r="960" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -26453,7 +26497,7 @@
       <c r="X960" s="1"/>
       <c r="Y960" s="1"/>
     </row>
-    <row r="961" spans="1:25" ht="12.75">
+    <row r="961" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -26480,7 +26524,7 @@
       <c r="X961" s="1"/>
       <c r="Y961" s="1"/>
     </row>
-    <row r="962" spans="1:25" ht="12.75">
+    <row r="962" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -26507,7 +26551,7 @@
       <c r="X962" s="1"/>
       <c r="Y962" s="1"/>
     </row>
-    <row r="963" spans="1:25" ht="12.75">
+    <row r="963" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -26534,7 +26578,7 @@
       <c r="X963" s="1"/>
       <c r="Y963" s="1"/>
     </row>
-    <row r="964" spans="1:25" ht="12.75">
+    <row r="964" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -26561,7 +26605,7 @@
       <c r="X964" s="1"/>
       <c r="Y964" s="1"/>
     </row>
-    <row r="965" spans="1:25" ht="12.75">
+    <row r="965" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -26588,7 +26632,7 @@
       <c r="X965" s="1"/>
       <c r="Y965" s="1"/>
     </row>
-    <row r="966" spans="1:25" ht="12.75">
+    <row r="966" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -26615,7 +26659,7 @@
       <c r="X966" s="1"/>
       <c r="Y966" s="1"/>
     </row>
-    <row r="967" spans="1:25" ht="12.75">
+    <row r="967" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -26642,7 +26686,7 @@
       <c r="X967" s="1"/>
       <c r="Y967" s="1"/>
     </row>
-    <row r="968" spans="1:25" ht="12.75">
+    <row r="968" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -26669,7 +26713,7 @@
       <c r="X968" s="1"/>
       <c r="Y968" s="1"/>
     </row>
-    <row r="969" spans="1:25" ht="12.75">
+    <row r="969" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -26696,7 +26740,7 @@
       <c r="X969" s="1"/>
       <c r="Y969" s="1"/>
     </row>
-    <row r="970" spans="1:25" ht="12.75">
+    <row r="970" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -26723,7 +26767,7 @@
       <c r="X970" s="1"/>
       <c r="Y970" s="1"/>
     </row>
-    <row r="971" spans="1:25" ht="12.75">
+    <row r="971" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -26750,7 +26794,7 @@
       <c r="X971" s="1"/>
       <c r="Y971" s="1"/>
     </row>
-    <row r="972" spans="1:25" ht="12.75">
+    <row r="972" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -26777,7 +26821,7 @@
       <c r="X972" s="1"/>
       <c r="Y972" s="1"/>
     </row>
-    <row r="973" spans="1:25" ht="12.75">
+    <row r="973" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -26804,7 +26848,7 @@
       <c r="X973" s="1"/>
       <c r="Y973" s="1"/>
     </row>
-    <row r="974" spans="1:25" ht="12.75">
+    <row r="974" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -26831,7 +26875,7 @@
       <c r="X974" s="1"/>
       <c r="Y974" s="1"/>
     </row>
-    <row r="975" spans="1:25" ht="12.75">
+    <row r="975" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -26858,7 +26902,7 @@
       <c r="X975" s="1"/>
       <c r="Y975" s="1"/>
     </row>
-    <row r="976" spans="1:25" ht="12.75">
+    <row r="976" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -26885,7 +26929,7 @@
       <c r="X976" s="1"/>
       <c r="Y976" s="1"/>
     </row>
-    <row r="977" spans="1:25" ht="12.75">
+    <row r="977" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
